--- a/vnadditivedb.xlsx
+++ b/vnadditivedb.xlsx
@@ -20,9 +20,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="1237">
-  <si>
-    <t>INS</t>
-  </si>
   <si>
     <t>100(i)</t>
   </si>
@@ -4302,6 +4299,9 @@
   </si>
   <si>
     <t>note_explanation</t>
+  </si>
+  <si>
+    <t>ins</t>
   </si>
 </sst>
 </file>
@@ -4777,75 +4777,75 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>1236</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1075</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="13" t="s">
         <v>1077</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="6" t="s">
         <v>1078</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="17" t="s">
         <v>1079</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>1081</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>1236</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="C2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>3</v>
-      </c>
       <c r="E2" s="25" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>1032</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>1033</v>
       </c>
       <c r="G2" s="23">
         <v>150</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="I2" s="24"/>
       <c r="J2" s="22" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>2</v>
-      </c>
       <c r="C3" s="22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="25"/>
@@ -4855,19 +4855,19 @@
         <v>52</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>2</v>
-      </c>
       <c r="C4" s="22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="25"/>
@@ -4877,26 +4877,26 @@
         <v>402</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>2</v>
-      </c>
       <c r="C5" s="22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="25">
         <v>12.5</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G5" s="23">
         <v>50</v>
@@ -4905,22 +4905,22 @@
         <v>99</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="8"/>
@@ -4928,27 +4928,27 @@
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>1032</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>1033</v>
       </c>
       <c r="G7" s="20">
         <v>300</v>
@@ -4957,28 +4957,28 @@
         <v>52</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="16" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>1071</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>1072</v>
       </c>
       <c r="G8" s="20">
         <v>300</v>
@@ -4989,20 +4989,20 @@
     </row>
     <row r="9" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>1073</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>1074</v>
       </c>
       <c r="G9" s="20">
         <v>300</v>
@@ -5013,20 +5013,20 @@
     </row>
     <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F10" s="27" t="s">
         <v>1084</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>1085</v>
       </c>
       <c r="G10" s="28">
         <v>300</v>
@@ -5037,20 +5037,20 @@
     </row>
     <row r="11" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="26" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F11" s="27" t="s">
         <v>1086</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>1087</v>
       </c>
       <c r="G11" s="28">
         <v>300</v>
@@ -5061,20 +5061,20 @@
     </row>
     <row r="12" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="26" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>1088</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>1089</v>
       </c>
       <c r="G12" s="28">
         <v>300</v>
@@ -5085,20 +5085,20 @@
     </row>
     <row r="13" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="26" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F13" s="29" t="s">
         <v>1090</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>1091</v>
       </c>
       <c r="G13" s="28">
         <v>300</v>
@@ -5109,20 +5109,20 @@
     </row>
     <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="26" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F14" s="29" t="s">
         <v>1092</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>1093</v>
       </c>
       <c r="G14" s="28">
         <v>300</v>
@@ -5133,20 +5133,20 @@
     </row>
     <row r="15" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="26" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G15" s="28">
         <v>300</v>
@@ -5157,20 +5157,20 @@
     </row>
     <row r="16" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F16" s="27" t="s">
         <v>1096</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>1097</v>
       </c>
       <c r="G16" s="32">
         <v>300</v>
@@ -5181,20 +5181,20 @@
     </row>
     <row r="17" spans="1:10" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G17" s="32">
         <v>300</v>
@@ -5205,20 +5205,20 @@
     </row>
     <row r="18" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="26" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G18" s="32">
         <v>300</v>
@@ -5229,19 +5229,19 @@
     </row>
     <row r="19" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E19" s="26" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G19" s="32">
         <v>500</v>
@@ -5252,38 +5252,38 @@
     </row>
     <row r="20" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E20" s="26" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="27" t="s">
         <v>1101</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>1102</v>
       </c>
       <c r="G20" s="32">
         <v>300</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="27"/>
@@ -5292,19 +5292,19 @@
         <v>4</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
@@ -5313,25 +5313,25 @@
         <v>16</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E23" s="26" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F23" s="27" t="s">
         <v>1104</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>1105</v>
       </c>
       <c r="G23" s="32">
         <v>300</v>
@@ -5340,25 +5340,25 @@
         <v>267</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E24" s="26" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F24" s="27" t="s">
         <v>1106</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>1107</v>
       </c>
       <c r="G24" s="32">
         <v>200</v>
@@ -5369,19 +5369,19 @@
     </row>
     <row r="25" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E25" s="26" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F25" s="27" t="s">
         <v>1108</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>1109</v>
       </c>
       <c r="G25" s="32">
         <v>500</v>
@@ -5392,19 +5392,19 @@
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E26" s="26" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F26" s="27" t="s">
         <v>1110</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>1111</v>
       </c>
       <c r="G26" s="32">
         <v>300</v>
@@ -5415,19 +5415,19 @@
     </row>
     <row r="27" spans="1:10" ht="75" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E27" s="26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F27" s="27" t="s">
         <v>1112</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>1113</v>
       </c>
       <c r="G27" s="32">
         <v>300</v>
@@ -5436,25 +5436,25 @@
         <v>182</v>
       </c>
       <c r="I27" s="35" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E28" s="26" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F28" s="27" t="s">
         <v>1114</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>1115</v>
       </c>
       <c r="G28" s="32">
         <v>300</v>
@@ -5465,19 +5465,19 @@
     </row>
     <row r="29" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E29" s="26" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F29" s="27" t="s">
         <v>1116</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>1117</v>
       </c>
       <c r="G29" s="32">
         <v>500</v>
@@ -5488,19 +5488,19 @@
     </row>
     <row r="30" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E30" s="26" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F30" s="27" t="s">
         <v>1118</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>1119</v>
       </c>
       <c r="G30" s="32">
         <v>300</v>
@@ -5511,38 +5511,38 @@
     </row>
     <row r="31" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E31" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F31" s="27" t="s">
         <v>1120</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>1121</v>
       </c>
       <c r="G31" s="32">
         <v>300</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E32" s="26"/>
       <c r="F32" s="27"/>
@@ -5551,19 +5551,19 @@
         <v>4</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
@@ -5572,25 +5572,25 @@
         <v>16</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E34" s="26" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F34" s="27" t="s">
         <v>1122</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>1123</v>
       </c>
       <c r="G34" s="32">
         <v>500</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="35" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E35" s="26" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F35" s="27" t="s">
         <v>1124</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>1125</v>
       </c>
       <c r="G35" s="32">
         <v>300</v>
@@ -5622,25 +5622,25 @@
         <v>92</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E36" s="26" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F36" s="27" t="s">
         <v>1126</v>
-      </c>
-      <c r="F36" s="27" t="s">
-        <v>1127</v>
       </c>
       <c r="G36" s="32">
         <v>500</v>
@@ -5651,19 +5651,19 @@
     </row>
     <row r="37" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E37" s="26" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F37" s="27" t="s">
         <v>1128</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>1129</v>
       </c>
       <c r="G37" s="32">
         <v>1000</v>
@@ -5674,46 +5674,46 @@
     </row>
     <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E38" s="26" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G38" s="32">
         <v>1000</v>
       </c>
       <c r="H38" s="33" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="I38" s="31" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E39" s="26" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G39" s="32">
         <v>1000</v>
@@ -5724,19 +5724,19 @@
     </row>
     <row r="40" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E40" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G40" s="32">
         <v>1000</v>
@@ -5747,19 +5747,19 @@
     </row>
     <row r="41" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E41" s="26" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G41" s="32">
         <v>300</v>
@@ -5770,19 +5770,19 @@
     </row>
     <row r="42" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E42" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F42" s="27" t="s">
         <v>1135</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>1136</v>
       </c>
       <c r="G42" s="32">
         <v>300</v>
@@ -5791,25 +5791,25 @@
         <v>153</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E43" s="26" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G43" s="32">
         <v>300</v>
@@ -5820,19 +5820,19 @@
     </row>
     <row r="44" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E44" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G44" s="32">
         <v>300</v>
@@ -5843,19 +5843,19 @@
     </row>
     <row r="45" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E45" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F45" s="27" t="s">
         <v>1139</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>1140</v>
       </c>
       <c r="G45" s="32">
         <v>50</v>
@@ -5866,19 +5866,19 @@
     </row>
     <row r="46" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E46" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G46" s="32">
         <v>300</v>
@@ -5889,38 +5889,38 @@
     </row>
     <row r="47" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E47" s="26" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G47" s="32">
         <v>1000</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
     <row r="48" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="27"/>
@@ -5929,86 +5929,86 @@
         <v>16</v>
       </c>
       <c r="I48" s="30" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="27"/>
       <c r="G49" s="32"/>
       <c r="H49" s="33" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I49" s="31" t="s">
         <v>1229</v>
-      </c>
-      <c r="I49" s="31" t="s">
-        <v>1230</v>
       </c>
       <c r="J49" s="2"/>
     </row>
     <row r="50" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E50" s="26"/>
       <c r="F50" s="27"/>
       <c r="G50" s="32"/>
       <c r="H50" s="33" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I50" s="31" t="s">
         <v>1231</v>
-      </c>
-      <c r="I50" s="31" t="s">
-        <v>1232</v>
       </c>
       <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E51" s="26" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G51" s="32">
         <v>1000</v>
       </c>
       <c r="H51" s="33" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="C52" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E52" s="26"/>
       <c r="F52" s="27"/>
@@ -6017,88 +6017,88 @@
         <v>16</v>
       </c>
       <c r="I52" s="30" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E53" s="26"/>
       <c r="F53" s="27"/>
       <c r="G53" s="32"/>
       <c r="H53" s="33" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I53" s="31" t="s">
         <v>1225</v>
-      </c>
-      <c r="I53" s="31" t="s">
-        <v>1226</v>
       </c>
       <c r="J53" s="2"/>
     </row>
     <row r="54" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E54" s="26"/>
       <c r="F54" s="27"/>
       <c r="G54" s="32"/>
       <c r="H54" s="33" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I54" s="31" t="s">
         <v>1227</v>
-      </c>
-      <c r="I54" s="31" t="s">
-        <v>1228</v>
       </c>
       <c r="J54" s="2"/>
     </row>
     <row r="55" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E55" s="26"/>
       <c r="F55" s="27"/>
       <c r="G55" s="32"/>
       <c r="H55" s="33" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I55" s="31" t="s">
         <v>1233</v>
-      </c>
-      <c r="I55" s="31" t="s">
-        <v>1234</v>
       </c>
       <c r="J55" s="2"/>
     </row>
     <row r="56" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E56" s="26" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G56" s="32">
         <v>1000</v>
@@ -6107,44 +6107,44 @@
         <v>16</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="J56" s="2"/>
     </row>
     <row r="57" spans="1:10" ht="281.25" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E57" s="26" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F57" s="27" t="s">
         <v>1147</v>
-      </c>
-      <c r="F57" s="27" t="s">
-        <v>1148</v>
       </c>
       <c r="G57" s="32">
         <v>1000</v>
       </c>
       <c r="H57" s="33" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E58" s="26"/>
       <c r="F58" s="27"/>
@@ -6153,71 +6153,71 @@
         <v>95</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="J58" s="2"/>
     </row>
     <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E59" s="26"/>
       <c r="F59" s="27"/>
       <c r="G59" s="32"/>
       <c r="H59" s="33" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>1224</v>
       </c>
       <c r="J59" s="2"/>
     </row>
     <row r="60" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E60" s="26" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F60" s="27" t="s">
         <v>1150</v>
-      </c>
-      <c r="F60" s="27" t="s">
-        <v>1151</v>
       </c>
       <c r="G60" s="32">
         <v>300</v>
       </c>
       <c r="H60" s="33" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
     <row r="61" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E61" s="26" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F61" s="27" t="s">
         <v>1153</v>
-      </c>
-      <c r="F61" s="27" t="s">
-        <v>1154</v>
       </c>
       <c r="G61" s="32">
         <v>300</v>
@@ -6230,19 +6230,19 @@
     </row>
     <row r="62" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="C62" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E62" s="26" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F62" s="27" t="s">
         <v>1155</v>
-      </c>
-      <c r="F62" s="27" t="s">
-        <v>1156</v>
       </c>
       <c r="G62" s="32">
         <v>300</v>
@@ -6255,19 +6255,19 @@
     </row>
     <row r="63" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="C63" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E63" s="26" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F63" s="27" t="s">
         <v>1157</v>
-      </c>
-      <c r="F63" s="27" t="s">
-        <v>1158</v>
       </c>
       <c r="G63" s="32">
         <v>300</v>
@@ -6278,19 +6278,19 @@
     </row>
     <row r="64" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E64" s="26" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F64" s="27" t="s">
         <v>1159</v>
-      </c>
-      <c r="F64" s="27" t="s">
-        <v>1160</v>
       </c>
       <c r="G64" s="32">
         <v>300</v>
@@ -6303,44 +6303,44 @@
     </row>
     <row r="65" spans="1:10" ht="225" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E65" s="26" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F65" s="27" t="s">
         <v>1161</v>
-      </c>
-      <c r="F65" s="27" t="s">
-        <v>1162</v>
       </c>
       <c r="G65" s="32">
         <v>300</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
     <row r="66" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E66" s="26" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F66" s="27" t="s">
         <v>1164</v>
-      </c>
-      <c r="F66" s="27" t="s">
-        <v>1165</v>
       </c>
       <c r="G66" s="32">
         <v>300</v>
@@ -6353,19 +6353,19 @@
     </row>
     <row r="67" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="C67" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E67" s="26" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F67" s="27" t="s">
         <v>1166</v>
-      </c>
-      <c r="F67" s="27" t="s">
-        <v>1167</v>
       </c>
       <c r="G67" s="32">
         <v>300</v>
@@ -6378,44 +6378,44 @@
     </row>
     <row r="68" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E68" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F68" s="27" t="s">
         <v>1168</v>
-      </c>
-      <c r="F68" s="27" t="s">
-        <v>1169</v>
       </c>
       <c r="G68" s="32">
         <v>300</v>
       </c>
       <c r="H68" s="33" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E69" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F69" s="27" t="s">
         <v>1171</v>
-      </c>
-      <c r="F69" s="27" t="s">
-        <v>1172</v>
       </c>
       <c r="G69" s="32">
         <v>300</v>
@@ -6426,44 +6426,44 @@
     </row>
     <row r="70" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="C70" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E70" s="26" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F70" s="27" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G70" s="32">
         <v>500</v>
       </c>
       <c r="H70" s="33" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
     <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="C71" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E71" s="26">
         <v>10.1</v>
       </c>
       <c r="F71" s="27" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G71" s="32">
         <v>300</v>
@@ -6476,19 +6476,19 @@
     </row>
     <row r="72" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E72" s="26">
         <v>10.4</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G72" s="32">
         <v>300</v>
@@ -6499,19 +6499,19 @@
     </row>
     <row r="73" spans="1:10" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="C73" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E73" s="26">
         <v>11.3</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G73" s="32">
         <v>300</v>
@@ -6522,19 +6522,19 @@
     </row>
     <row r="74" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="C74" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E74" s="26">
         <v>11.4</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G74" s="32">
         <v>300</v>
@@ -6545,19 +6545,19 @@
     </row>
     <row r="75" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="C75" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E75" s="26" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F75" s="27" t="s">
         <v>1179</v>
-      </c>
-      <c r="F75" s="27" t="s">
-        <v>1180</v>
       </c>
       <c r="G75" s="32">
         <v>350</v>
@@ -6568,19 +6568,19 @@
     </row>
     <row r="76" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="C76" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E76" s="26">
         <v>12.4</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G76" s="32">
         <v>300</v>
@@ -6591,19 +6591,19 @@
     </row>
     <row r="77" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="C77" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E77" s="26">
         <v>12.5</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G77" s="32">
         <v>200</v>
@@ -6616,44 +6616,44 @@
     </row>
     <row r="78" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E78" s="26">
         <v>12.6</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G78" s="32">
         <v>350</v>
       </c>
       <c r="H78" s="33" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
     </row>
     <row r="79" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="C79" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E79" s="26">
         <v>12.7</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G79" s="32">
         <v>300</v>
@@ -6664,19 +6664,19 @@
     </row>
     <row r="80" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E80" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F80" s="27" t="s">
         <v>1185</v>
-      </c>
-      <c r="F80" s="27" t="s">
-        <v>1186</v>
       </c>
       <c r="G80" s="32">
         <v>30</v>
@@ -6687,19 +6687,19 @@
     </row>
     <row r="81" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E81" s="26">
         <v>13.3</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G81" s="32">
         <v>300</v>
@@ -6710,19 +6710,19 @@
     </row>
     <row r="82" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="C82" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E82" s="26">
         <v>13.4</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G82" s="32">
         <v>300</v>
@@ -6733,19 +6733,19 @@
     </row>
     <row r="83" spans="1:10" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="C83" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E83" s="26">
         <v>13.5</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G83" s="32">
         <v>300</v>
@@ -6756,19 +6756,19 @@
     </row>
     <row r="84" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="C84" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E84" s="26">
         <v>13.6</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G84" s="32">
         <v>300</v>
@@ -6779,19 +6779,19 @@
     </row>
     <row r="85" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="C85" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C85" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E85" s="26" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F85" s="27" t="s">
         <v>1191</v>
-      </c>
-      <c r="F85" s="27" t="s">
-        <v>1192</v>
       </c>
       <c r="G85" s="32">
         <v>50</v>
@@ -6802,19 +6802,19 @@
     </row>
     <row r="86" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E86" s="26" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F86" s="27" t="s">
         <v>1193</v>
-      </c>
-      <c r="F86" s="27" t="s">
-        <v>1194</v>
       </c>
       <c r="G86" s="32">
         <v>300</v>
@@ -6825,19 +6825,19 @@
     </row>
     <row r="87" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="C87" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E87" s="26" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F87" s="27" t="s">
         <v>1195</v>
-      </c>
-      <c r="F87" s="27" t="s">
-        <v>1196</v>
       </c>
       <c r="G87" s="32">
         <v>300</v>
@@ -6848,19 +6848,19 @@
     </row>
     <row r="88" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="C88" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="E88" s="26" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F88" s="27" t="s">
         <v>1197</v>
-      </c>
-      <c r="F88" s="27" t="s">
-        <v>1198</v>
       </c>
       <c r="G88" s="32">
         <v>100</v>
@@ -6871,19 +6871,19 @@
     </row>
     <row r="89" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="C89" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E89" s="26">
         <v>15.1</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G89" s="32">
         <v>1000</v>
@@ -6894,19 +6894,19 @@
     </row>
     <row r="90" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="C90" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E90" s="26">
         <v>15.2</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G90" s="32">
         <v>1000</v>
@@ -6917,16 +6917,16 @@
     </row>
     <row r="91" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="13"/>
       <c r="F91" s="2"/>
@@ -6937,16 +6937,16 @@
     </row>
     <row r="92" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>1038</v>
-      </c>
       <c r="D92" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="13"/>
       <c r="F92" s="2"/>
@@ -6960,13 +6960,13 @@
         <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D93" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" s="13"/>
       <c r="F93" s="2"/>
@@ -6980,13 +6980,13 @@
         <v>104</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D94" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="13"/>
       <c r="F94" s="2"/>
@@ -7000,13 +7000,13 @@
         <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="13"/>
       <c r="F95" s="2"/>
@@ -7020,13 +7020,13 @@
         <v>120</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D96" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="13"/>
       <c r="F96" s="2"/>
@@ -7040,13 +7040,13 @@
         <v>122</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="13"/>
       <c r="F97" s="2"/>
@@ -7060,13 +7060,13 @@
         <v>123</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="13"/>
       <c r="F98" s="2"/>
@@ -7080,13 +7080,13 @@
         <v>124</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="13"/>
       <c r="F99" s="2"/>
@@ -7100,13 +7100,13 @@
         <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D100" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="13"/>
       <c r="F100" s="2"/>
@@ -7120,13 +7120,13 @@
         <v>129</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" s="13"/>
       <c r="F101" s="2"/>
@@ -7140,13 +7140,13 @@
         <v>132</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="D102" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="13"/>
       <c r="F102" s="2"/>
@@ -7160,13 +7160,13 @@
         <v>133</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" s="13"/>
       <c r="F103" s="2"/>
@@ -7180,13 +7180,13 @@
         <v>140</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D104" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" s="13"/>
       <c r="F104" s="2"/>
@@ -7197,16 +7197,16 @@
     </row>
     <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" s="13"/>
       <c r="F105" s="2"/>
@@ -7217,16 +7217,16 @@
     </row>
     <row r="106" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D106" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" s="13"/>
       <c r="F106" s="2"/>
@@ -7240,13 +7240,13 @@
         <v>143</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" s="13"/>
       <c r="F107" s="2"/>
@@ -7257,16 +7257,16 @@
     </row>
     <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="D108" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" s="13"/>
       <c r="F108" s="2"/>
@@ -7277,16 +7277,16 @@
     </row>
     <row r="109" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="D109" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" s="13"/>
       <c r="F109" s="2"/>
@@ -7297,16 +7297,16 @@
     </row>
     <row r="110" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="D110" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="13"/>
       <c r="F110" s="2"/>
@@ -7317,16 +7317,16 @@
     </row>
     <row r="111" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D111" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" s="13"/>
       <c r="F111" s="2"/>
@@ -7340,13 +7340,13 @@
         <v>151</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" s="13"/>
       <c r="F112" s="2"/>
@@ -7360,13 +7360,13 @@
         <v>153</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D113" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" s="13"/>
       <c r="F113" s="2"/>
@@ -7380,13 +7380,13 @@
         <v>155</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="13"/>
       <c r="F114" s="2"/>
@@ -7397,16 +7397,16 @@
     </row>
     <row r="115" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="D115" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115" s="13"/>
       <c r="F115" s="2"/>
@@ -7417,16 +7417,16 @@
     </row>
     <row r="116" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D116" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116" s="13"/>
       <c r="F116" s="2"/>
@@ -7437,16 +7437,16 @@
     </row>
     <row r="117" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>1040</v>
-      </c>
       <c r="D117" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" s="13"/>
       <c r="F117" s="2"/>
@@ -7457,16 +7457,16 @@
     </row>
     <row r="118" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="D118" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" s="13"/>
       <c r="F118" s="2"/>
@@ -7477,16 +7477,16 @@
     </row>
     <row r="119" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" s="13"/>
       <c r="F119" s="2"/>
@@ -7497,16 +7497,16 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E120" s="13"/>
       <c r="F120" s="2"/>
@@ -7517,16 +7517,16 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D121" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" s="13"/>
       <c r="F121" s="2"/>
@@ -7537,16 +7537,16 @@
     </row>
     <row r="122" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D122" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" s="13"/>
       <c r="F122" s="2"/>
@@ -7557,16 +7557,16 @@
     </row>
     <row r="123" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>1042</v>
-      </c>
       <c r="D123" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" s="13"/>
       <c r="F123" s="2"/>
@@ -7577,16 +7577,16 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D124" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124" s="13"/>
       <c r="F124" s="2"/>
@@ -7597,16 +7597,16 @@
     </row>
     <row r="125" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D125" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="13"/>
       <c r="F125" s="2"/>
@@ -7617,16 +7617,16 @@
     </row>
     <row r="126" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>1044</v>
-      </c>
       <c r="D126" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" s="13"/>
       <c r="F126" s="2"/>
@@ -7637,16 +7637,16 @@
     </row>
     <row r="127" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>1046</v>
-      </c>
       <c r="D127" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="13"/>
       <c r="F127" s="2"/>
@@ -7657,16 +7657,16 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" s="13"/>
       <c r="F128" s="2"/>
@@ -7677,16 +7677,16 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D129" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" s="13"/>
       <c r="F129" s="2"/>
@@ -7700,13 +7700,13 @@
         <v>162</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" s="13"/>
       <c r="F130" s="2"/>
@@ -7717,16 +7717,16 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D131" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131" s="13"/>
       <c r="F131" s="2"/>
@@ -7737,16 +7737,16 @@
     </row>
     <row r="132" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="D132" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="13"/>
       <c r="F132" s="2"/>
@@ -7757,16 +7757,16 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D133" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" s="13"/>
       <c r="F133" s="2"/>
@@ -7777,16 +7777,16 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="D134" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" s="13"/>
       <c r="F134" s="2"/>
@@ -7797,16 +7797,16 @@
     </row>
     <row r="135" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D135" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="13"/>
       <c r="F135" s="2"/>
@@ -7817,16 +7817,16 @@
     </row>
     <row r="136" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D136" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="13"/>
       <c r="F136" s="2"/>
@@ -7837,16 +7837,16 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D137" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" s="13"/>
       <c r="F137" s="2"/>
@@ -7860,13 +7860,13 @@
         <v>164</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" s="13"/>
       <c r="F138" s="2"/>
@@ -7877,16 +7877,16 @@
     </row>
     <row r="139" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="D139" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E139" s="13"/>
       <c r="F139" s="2"/>
@@ -7900,13 +7900,13 @@
         <v>171</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="D140" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" s="13"/>
       <c r="F140" s="2"/>
@@ -7917,16 +7917,16 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D141" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" s="13"/>
       <c r="F141" s="2"/>
@@ -7937,16 +7937,16 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="D142" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" s="13"/>
       <c r="F142" s="2"/>
@@ -7957,16 +7957,16 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="C143" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D143" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" s="13"/>
       <c r="F143" s="2"/>
@@ -7980,13 +7980,13 @@
         <v>181</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="D144" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E144" s="13"/>
       <c r="F144" s="2"/>
@@ -8000,13 +8000,13 @@
         <v>200</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="E145" s="13"/>
       <c r="F145" s="2"/>
@@ -8020,13 +8020,13 @@
         <v>201</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="D146" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E146" s="13"/>
       <c r="F146" s="2"/>
@@ -8040,13 +8040,13 @@
         <v>202</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="D147" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E147" s="13"/>
       <c r="F147" s="2"/>
@@ -8060,13 +8060,13 @@
         <v>203</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D148" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E148" s="13"/>
       <c r="F148" s="2"/>
@@ -8080,13 +8080,13 @@
         <v>210</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D149" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E149" s="13"/>
       <c r="F149" s="2"/>
@@ -8100,13 +8100,13 @@
         <v>211</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="D150" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E150" s="13"/>
       <c r="F150" s="2"/>
@@ -8120,13 +8120,13 @@
         <v>212</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D151" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E151" s="13"/>
       <c r="F151" s="2"/>
@@ -8140,13 +8140,13 @@
         <v>213</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D152" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E152" s="13"/>
       <c r="F152" s="2"/>
@@ -8160,13 +8160,13 @@
         <v>214</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="D153" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E153" s="13"/>
       <c r="F153" s="2"/>
@@ -8180,13 +8180,13 @@
         <v>218</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="D154" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -8194,13 +8194,13 @@
         <v>220</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="D155" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -8208,13 +8208,13 @@
         <v>221</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="D156" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -8222,13 +8222,13 @@
         <v>222</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="D157" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -8236,13 +8236,13 @@
         <v>223</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="D158" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -8250,13 +8250,13 @@
         <v>224</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D159" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -8264,13 +8264,13 @@
         <v>225</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="D160" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -8278,13 +8278,13 @@
         <v>231</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8292,13 +8292,13 @@
         <v>232</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="D162" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -8306,13 +8306,13 @@
         <v>234</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -8320,13 +8320,13 @@
         <v>235</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -8334,13 +8334,13 @@
         <v>239</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="D165" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -8348,13 +8348,13 @@
         <v>242</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="D166" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8362,13 +8362,13 @@
         <v>243</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="D167" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8376,13 +8376,13 @@
         <v>249</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="D168" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8390,13 +8390,13 @@
         <v>250</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C169" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="D169" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8404,13 +8404,13 @@
         <v>251</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="D170" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8418,55 +8418,55 @@
         <v>260</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="D171" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="C172" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="D172" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="C173" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="D173" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="C174" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="D174" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -8474,13 +8474,13 @@
         <v>263</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="D175" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -8488,13 +8488,13 @@
         <v>266</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="D176" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -8502,13 +8502,13 @@
         <v>270</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="D177" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -8516,13 +8516,13 @@
         <v>280</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D178" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -8530,13 +8530,13 @@
         <v>281</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D179" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -8544,13 +8544,13 @@
         <v>282</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="D180" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -8558,13 +8558,13 @@
         <v>283</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="D181" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -8572,13 +8572,13 @@
         <v>290</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="D182" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8586,13 +8586,13 @@
         <v>296</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="D183" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -8600,13 +8600,13 @@
         <v>297</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D184" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -8614,13 +8614,13 @@
         <v>300</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="D185" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -8628,13 +8628,13 @@
         <v>301</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="D186" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -8642,13 +8642,13 @@
         <v>302</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="D187" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -8656,13 +8656,13 @@
         <v>304</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="D188" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -8670,55 +8670,55 @@
         <v>305</v>
       </c>
       <c r="B189" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D189" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="C190" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="D190" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="C191" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C191" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="D191" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="C192" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="D192" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -8726,13 +8726,13 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="D193" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -8740,13 +8740,13 @@
         <v>314</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="D194" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8754,13 +8754,13 @@
         <v>315</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="D195" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -8768,13 +8768,13 @@
         <v>316</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="D196" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8782,13 +8782,13 @@
         <v>319</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D197" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8796,13 +8796,13 @@
         <v>320</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="D198" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8810,27 +8810,27 @@
         <v>321</v>
       </c>
       <c r="B199" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D199" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="C200" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D200" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -8838,13 +8838,13 @@
         <v>325</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="D201" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -8852,13 +8852,13 @@
         <v>326</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="D202" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -8866,13 +8866,13 @@
         <v>327</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="D203" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8880,13 +8880,13 @@
         <v>329</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="D204" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -8894,97 +8894,97 @@
         <v>330</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="D205" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="C206" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="D206" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="C207" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C207" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="D207" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B208" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="C208" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C208" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="D208" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C209" s="2" t="s">
+      <c r="D209" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="D210" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="D211" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -8992,27 +8992,27 @@
         <v>334</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="D212" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B213" s="2" t="s">
+      <c r="C213" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="D213" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -9020,13 +9020,13 @@
         <v>337</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C214" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="D214" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9034,251 +9034,251 @@
         <v>338</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="D215" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="C216" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="D216" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B217" s="2" t="s">
+      <c r="C217" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="D217" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="C218" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="D218" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="C219" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="D219" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="C220" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="D220" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="C221" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C221" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="D221" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="C222" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="D222" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="C223" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="D223" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="C224" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="D224" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="C225" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="D225" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="C226" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="D226" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="C227" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="D227" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="D228" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="D229" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="C230" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="D230" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="D231" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="C232" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C232" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="D232" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9286,13 +9286,13 @@
         <v>353</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="D233" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -9300,13 +9300,13 @@
         <v>355</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C234" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="D234" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -9314,13 +9314,13 @@
         <v>363</v>
       </c>
       <c r="B235" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="C235" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C235" s="37" t="s">
-        <v>378</v>
-      </c>
       <c r="D235" s="37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -9331,16 +9331,16 @@
     </row>
     <row r="237" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="D237" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -9348,13 +9348,13 @@
         <v>365</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="D238" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -9362,13 +9362,13 @@
         <v>380</v>
       </c>
       <c r="B239" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C239" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="D239" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -9376,13 +9376,13 @@
         <v>381</v>
       </c>
       <c r="B240" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="D240" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9390,13 +9390,13 @@
         <v>384</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="D241" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9404,13 +9404,13 @@
         <v>385</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="D242" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -9418,13 +9418,13 @@
         <v>386</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="D243" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -9432,13 +9432,13 @@
         <v>388</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="D244" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -9446,13 +9446,13 @@
         <v>389</v>
       </c>
       <c r="B245" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C245" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="D245" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -9460,13 +9460,13 @@
         <v>392</v>
       </c>
       <c r="B246" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C246" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="D246" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="105" x14ac:dyDescent="0.25">
@@ -9474,13 +9474,13 @@
         <v>400</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="D247" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="105" x14ac:dyDescent="0.25">
@@ -9488,13 +9488,13 @@
         <v>401</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C248" s="2" t="s">
+      <c r="D248" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="105" x14ac:dyDescent="0.25">
@@ -9502,13 +9502,13 @@
         <v>402</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C249" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="D249" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="105" x14ac:dyDescent="0.25">
@@ -9516,13 +9516,13 @@
         <v>403</v>
       </c>
       <c r="B250" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C250" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="D250" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="90" x14ac:dyDescent="0.25">
@@ -9530,13 +9530,13 @@
         <v>404</v>
       </c>
       <c r="B251" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="D251" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -9544,13 +9544,13 @@
         <v>405</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="D252" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -9558,13 +9558,13 @@
         <v>406</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="D253" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -9572,27 +9572,27 @@
         <v>407</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="C255" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="D255" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9600,13 +9600,13 @@
         <v>410</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C256" s="2" t="s">
+      <c r="D256" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9614,13 +9614,13 @@
         <v>412</v>
       </c>
       <c r="B257" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C257" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="D257" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9628,13 +9628,13 @@
         <v>413</v>
       </c>
       <c r="B258" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="D258" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -9642,13 +9642,13 @@
         <v>414</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="D259" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9656,13 +9656,13 @@
         <v>415</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="D260" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9670,13 +9670,13 @@
         <v>416</v>
       </c>
       <c r="B261" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C261" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="D261" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9684,13 +9684,13 @@
         <v>417</v>
       </c>
       <c r="B262" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C262" s="2" t="s">
+      <c r="D262" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9698,41 +9698,41 @@
         <v>418</v>
       </c>
       <c r="B263" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C263" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="D263" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="C264" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="C265" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C265" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="D265" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -9740,13 +9740,13 @@
         <v>421</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="D266" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9754,13 +9754,13 @@
         <v>422</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9768,13 +9768,13 @@
         <v>423</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C268" s="2" t="s">
+      <c r="D268" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9782,13 +9782,13 @@
         <v>424</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D269" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -9796,13 +9796,13 @@
         <v>425</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="D270" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9810,13 +9810,13 @@
         <v>427</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="D271" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9824,13 +9824,13 @@
         <v>430</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C272" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="D272" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9838,13 +9838,13 @@
         <v>431</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C273" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="D273" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9852,13 +9852,13 @@
         <v>432</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C274" s="2" t="s">
+      <c r="D274" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9866,13 +9866,13 @@
         <v>433</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C275" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="D275" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9880,13 +9880,13 @@
         <v>434</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C276" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="D276" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9894,13 +9894,13 @@
         <v>435</v>
       </c>
       <c r="B277" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C277" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="D277" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9908,13 +9908,13 @@
         <v>436</v>
       </c>
       <c r="B278" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C278" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="D278" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -9922,13 +9922,13 @@
         <v>440</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="D279" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9936,13 +9936,13 @@
         <v>442</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="C280" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="D280" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -9950,223 +9950,223 @@
         <v>444</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C281" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="D281" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="C282" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C282" s="2" t="s">
-        <v>495</v>
-      </c>
       <c r="D282" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="C283" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="D283" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="C284" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C284" s="2" t="s">
+      <c r="D284" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="C285" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C285" s="2" t="s">
+      <c r="D285" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="C286" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="D286" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A287" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B287" s="2" t="s">
+      <c r="C287" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="D287" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="C288" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="D288" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B289" s="2" t="s">
+      <c r="C289" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="D289" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="C290" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="D290" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B291" s="2" t="s">
+      <c r="C291" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>529</v>
-      </c>
       <c r="D291" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="C292" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="D292" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B293" s="2" t="s">
+      <c r="C293" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C293" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="D293" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B294" s="2" t="s">
+      <c r="C294" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="D294" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C295" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="D295" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B296" s="2" t="s">
+      <c r="C296" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="D296" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10174,13 +10174,13 @@
         <v>455</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="D297" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10188,13 +10188,13 @@
         <v>457</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="C298" s="2" t="s">
-        <v>1048</v>
-      </c>
       <c r="D298" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10202,13 +10202,13 @@
         <v>458</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10216,41 +10216,41 @@
         <v>459</v>
       </c>
       <c r="B300" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D300" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B301" s="2" t="s">
+      <c r="C301" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="D301" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A302" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="C302" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="D302" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10258,13 +10258,13 @@
         <v>461</v>
       </c>
       <c r="B303" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D303" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10272,13 +10272,13 @@
         <v>462</v>
       </c>
       <c r="B304" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D304" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10286,13 +10286,13 @@
         <v>463</v>
       </c>
       <c r="B305" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D305" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="D305" s="3" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10300,13 +10300,13 @@
         <v>464</v>
       </c>
       <c r="B306" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D306" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10314,13 +10314,13 @@
         <v>465</v>
       </c>
       <c r="B307" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D307" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D307" s="3" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -10328,13 +10328,13 @@
         <v>466</v>
       </c>
       <c r="B308" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="C308" s="2" t="s">
+      <c r="D308" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10342,13 +10342,13 @@
         <v>467</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D309" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10356,13 +10356,13 @@
         <v>468</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="C310" s="2" t="s">
+      <c r="D310" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10370,55 +10370,55 @@
         <v>469</v>
       </c>
       <c r="B311" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C311" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="C311" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="D311" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A312" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="C312" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C312" s="2" t="s">
+      <c r="D312" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="C313" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="C313" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="D313" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A314" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="C314" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="C314" s="2" t="s">
+      <c r="D314" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="D314" s="3" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10426,69 +10426,69 @@
         <v>471</v>
       </c>
       <c r="B315" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C315" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C315" s="2" t="s">
+      <c r="D315" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A316" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="C316" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C316" s="2" t="s">
+      <c r="D316" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="D316" s="3" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A317" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="C317" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C317" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="D317" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A318" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="C318" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="C318" s="2" t="s">
+      <c r="D318" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="D318" s="3" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A319" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B319" s="2" t="s">
+      <c r="C319" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C319" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="D319" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10496,27 +10496,27 @@
         <v>473</v>
       </c>
       <c r="B320" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C320" s="2" t="s">
+      <c r="D320" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A321" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B321" s="2" t="s">
+      <c r="C321" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C321" s="2" t="s">
+      <c r="D321" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -10524,13 +10524,13 @@
         <v>474</v>
       </c>
       <c r="B322" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C322" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="C322" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="D322" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10538,13 +10538,13 @@
         <v>475</v>
       </c>
       <c r="B323" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C323" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="D323" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10552,13 +10552,13 @@
         <v>476</v>
       </c>
       <c r="B324" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C324" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="C324" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="D324" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10566,13 +10566,13 @@
         <v>477</v>
       </c>
       <c r="B325" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C325" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C325" s="2" t="s">
-        <v>625</v>
-      </c>
       <c r="D325" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -10580,13 +10580,13 @@
         <v>479</v>
       </c>
       <c r="B326" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C326" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="D326" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10594,41 +10594,41 @@
         <v>480</v>
       </c>
       <c r="B327" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C327" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C327" s="2" t="s">
+      <c r="D327" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="D327" s="3" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A328" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="C328" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C328" s="2" t="s">
+      <c r="D328" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="D328" s="3" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A329" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="C329" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="D329" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10636,13 +10636,13 @@
         <v>484</v>
       </c>
       <c r="B330" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C330" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="C330" s="2" t="s">
+      <c r="D330" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="D330" s="3" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10650,13 +10650,13 @@
         <v>491</v>
       </c>
       <c r="B331" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C331" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="C331" s="2" t="s">
-        <v>642</v>
-      </c>
       <c r="D331" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10664,13 +10664,13 @@
         <v>492</v>
       </c>
       <c r="B332" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C332" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C332" s="2" t="s">
-        <v>644</v>
-      </c>
       <c r="D332" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10678,13 +10678,13 @@
         <v>493</v>
       </c>
       <c r="B333" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C333" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C333" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="D333" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10692,13 +10692,13 @@
         <v>494</v>
       </c>
       <c r="B334" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C334" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C334" s="2" t="s">
-        <v>648</v>
-      </c>
       <c r="D334" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -10706,139 +10706,139 @@
         <v>495</v>
       </c>
       <c r="B335" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="C335" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="D335" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A336" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B336" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="B336" s="2" t="s">
+      <c r="C336" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="C336" s="2" t="s">
+      <c r="D336" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A337" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="B337" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B337" s="2" t="s">
+      <c r="C337" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="C337" s="2" t="s">
+      <c r="D337" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="D337" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A338" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="B338" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="B338" s="2" t="s">
+      <c r="C338" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="C338" s="2" t="s">
+      <c r="D338" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="D338" s="3" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A339" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="C339" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="C339" s="2" t="s">
+      <c r="D339" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="D339" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A340" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B340" s="2" t="s">
+      <c r="C340" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C340" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="D340" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A341" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="C341" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C341" s="2" t="s">
+      <c r="D341" s="3" t="s">
         <v>672</v>
-      </c>
-      <c r="D341" s="3" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A342" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="C342" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="D342" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="D342" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A343" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="C343" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="C343" s="2" t="s">
+      <c r="D343" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="D343" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A344" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="B344" s="2" t="s">
+      <c r="C344" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="C344" s="2" t="s">
+      <c r="D344" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -10846,13 +10846,13 @@
         <v>507</v>
       </c>
       <c r="B345" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C345" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="C345" s="2" t="s">
-        <v>687</v>
-      </c>
       <c r="D345" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10860,13 +10860,13 @@
         <v>508</v>
       </c>
       <c r="B346" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="C346" s="2" t="s">
+      <c r="D346" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="D346" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10874,13 +10874,13 @@
         <v>509</v>
       </c>
       <c r="B347" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="C347" s="2" t="s">
+      <c r="D347" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="D347" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -10888,13 +10888,13 @@
         <v>510</v>
       </c>
       <c r="B348" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C348" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="C348" s="2" t="s">
+      <c r="D348" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="D348" s="3" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10902,13 +10902,13 @@
         <v>511</v>
       </c>
       <c r="B349" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="C349" s="2" t="s">
+      <c r="D349" s="3" t="s">
         <v>698</v>
-      </c>
-      <c r="D349" s="3" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10916,69 +10916,69 @@
         <v>512</v>
       </c>
       <c r="B350" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="D350" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="D350" s="3" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B351" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="C351" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="C351" s="2" t="s">
-        <v>705</v>
-      </c>
       <c r="D351" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="B352" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="C352" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="C352" s="2" t="s">
-        <v>708</v>
-      </c>
       <c r="D352" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="B353" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="C353" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="C353" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="D353" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A354" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="B354" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="C354" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="C354" s="3" t="s">
-        <v>714</v>
-      </c>
       <c r="D354" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -10986,13 +10986,13 @@
         <v>516</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="C355" s="2" t="s">
+      <c r="D355" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="D355" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11000,13 +11000,13 @@
         <v>518</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="C356" s="2" t="s">
+      <c r="D356" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -11014,13 +11014,13 @@
         <v>523</v>
       </c>
       <c r="B357" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="C357" s="2" t="s">
+      <c r="D357" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="D357" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -11028,13 +11028,13 @@
         <v>524</v>
       </c>
       <c r="B358" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="C358" s="2" t="s">
-        <v>725</v>
-      </c>
       <c r="D358" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -11042,13 +11042,13 @@
         <v>525</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="C359" s="2" t="s">
-        <v>727</v>
-      </c>
       <c r="D359" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11056,13 +11056,13 @@
         <v>526</v>
       </c>
       <c r="B360" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C360" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="C360" s="2" t="s">
+      <c r="D360" s="3" t="s">
         <v>729</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -11070,13 +11070,13 @@
         <v>527</v>
       </c>
       <c r="B361" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="C361" s="2" t="s">
-        <v>732</v>
-      </c>
       <c r="D361" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11084,13 +11084,13 @@
         <v>528</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="C362" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="D362" s="3" t="s">
         <v>734</v>
-      </c>
-      <c r="D362" s="3" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11098,13 +11098,13 @@
         <v>529</v>
       </c>
       <c r="B363" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C363" s="2" t="s">
-        <v>737</v>
-      </c>
       <c r="D363" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11112,13 +11112,13 @@
         <v>530</v>
       </c>
       <c r="B364" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C364" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="C364" s="2" t="s">
+      <c r="D364" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="D364" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -11126,13 +11126,13 @@
         <v>535</v>
       </c>
       <c r="B365" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C365" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="C365" s="2" t="s">
-        <v>742</v>
-      </c>
       <c r="D365" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -11140,13 +11140,13 @@
         <v>536</v>
       </c>
       <c r="B366" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C366" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="C366" s="2" t="s">
-        <v>744</v>
-      </c>
       <c r="D366" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -11154,13 +11154,13 @@
         <v>538</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="C367" s="2" t="s">
-        <v>746</v>
-      </c>
       <c r="D367" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11168,41 +11168,41 @@
         <v>539</v>
       </c>
       <c r="B368" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C368" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="C368" s="2" t="s">
+      <c r="D368" s="3" t="s">
         <v>748</v>
-      </c>
-      <c r="D368" s="3" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A369" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="B369" s="2" t="s">
+      <c r="C369" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="C369" s="2" t="s">
+      <c r="D369" s="3" t="s">
         <v>752</v>
-      </c>
-      <c r="D369" s="3" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A370" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="B370" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B370" s="2" t="s">
+      <c r="C370" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="C370" s="2" t="s">
+      <c r="D370" s="3" t="s">
         <v>756</v>
-      </c>
-      <c r="D370" s="3" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -11210,13 +11210,13 @@
         <v>542</v>
       </c>
       <c r="B371" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="C371" s="2" t="s">
+      <c r="D371" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="D371" s="3" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11224,13 +11224,13 @@
         <v>551</v>
       </c>
       <c r="B372" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C372" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="C372" s="2" t="s">
+      <c r="D372" s="3" t="s">
         <v>762</v>
-      </c>
-      <c r="D372" s="3" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -11238,41 +11238,41 @@
         <v>552</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C373" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="C373" s="2" t="s">
-        <v>765</v>
-      </c>
       <c r="D373" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A374" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="B374" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="B374" s="2" t="s">
+      <c r="C374" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="C374" s="2" t="s">
-        <v>768</v>
-      </c>
       <c r="D374" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A375" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="B375" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B375" s="2" t="s">
+      <c r="C375" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="D375" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="D375" s="3" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -11280,13 +11280,13 @@
         <v>554</v>
       </c>
       <c r="B376" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C376" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="C376" s="2" t="s">
-        <v>774</v>
-      </c>
       <c r="D376" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11294,13 +11294,13 @@
         <v>575</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C377" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="C377" s="2" t="s">
+      <c r="D377" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="D377" s="3" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11308,13 +11308,13 @@
         <v>576</v>
       </c>
       <c r="B378" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C378" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="C378" s="2" t="s">
+      <c r="D378" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="D378" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11322,13 +11322,13 @@
         <v>577</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="C379" s="2" t="s">
+      <c r="D379" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11336,13 +11336,13 @@
         <v>578</v>
       </c>
       <c r="B380" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C380" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="C380" s="2" t="s">
+      <c r="D380" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -11350,13 +11350,13 @@
         <v>579</v>
       </c>
       <c r="B381" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C381" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="C381" s="2" t="s">
+      <c r="D381" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="D381" s="3" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11364,13 +11364,13 @@
         <v>580</v>
       </c>
       <c r="B382" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C382" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="C382" s="2" t="s">
+      <c r="D382" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="D382" s="3" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -11378,13 +11378,13 @@
         <v>585</v>
       </c>
       <c r="B383" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="C383" s="2" t="s">
-        <v>794</v>
-      </c>
       <c r="D383" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11392,13 +11392,13 @@
         <v>586</v>
       </c>
       <c r="B384" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C384" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="C384" s="2" t="s">
+      <c r="D384" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="D384" s="3" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -11406,13 +11406,13 @@
         <v>620</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="C385" s="2" t="s">
+      <c r="D385" s="3" t="s">
         <v>799</v>
-      </c>
-      <c r="D385" s="3" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -11420,13 +11420,13 @@
         <v>621</v>
       </c>
       <c r="B386" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C386" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="C386" s="2" t="s">
-        <v>802</v>
-      </c>
       <c r="D386" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11434,13 +11434,13 @@
         <v>622</v>
       </c>
       <c r="B387" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C387" s="2" t="s">
-        <v>804</v>
-      </c>
       <c r="D387" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -11448,13 +11448,13 @@
         <v>623</v>
       </c>
       <c r="B388" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C388" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="C388" s="2" t="s">
-        <v>806</v>
-      </c>
       <c r="D388" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11462,13 +11462,13 @@
         <v>624</v>
       </c>
       <c r="B389" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="C389" s="2" t="s">
-        <v>808</v>
-      </c>
       <c r="D389" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -11476,13 +11476,13 @@
         <v>625</v>
       </c>
       <c r="B390" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C390" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="C390" s="2" t="s">
-        <v>810</v>
-      </c>
       <c r="D390" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -11490,13 +11490,13 @@
         <v>626</v>
       </c>
       <c r="B391" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C391" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="C391" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="D391" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -11504,13 +11504,13 @@
         <v>627</v>
       </c>
       <c r="B392" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C392" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="C392" s="2" t="s">
-        <v>814</v>
-      </c>
       <c r="D392" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -11518,13 +11518,13 @@
         <v>628</v>
       </c>
       <c r="B393" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C393" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="C393" s="2" t="s">
-        <v>816</v>
-      </c>
       <c r="D393" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -11532,13 +11532,13 @@
         <v>629</v>
       </c>
       <c r="B394" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C394" s="2" t="s">
-        <v>818</v>
-      </c>
       <c r="D394" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -11546,13 +11546,13 @@
         <v>630</v>
       </c>
       <c r="B395" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C395" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="C395" s="2" t="s">
-        <v>820</v>
-      </c>
       <c r="D395" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -11560,13 +11560,13 @@
         <v>631</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C396" s="2" t="s">
-        <v>822</v>
-      </c>
       <c r="D396" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -11574,13 +11574,13 @@
         <v>632</v>
       </c>
       <c r="B397" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C397" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="C397" s="2" t="s">
-        <v>824</v>
-      </c>
       <c r="D397" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -11588,13 +11588,13 @@
         <v>633</v>
       </c>
       <c r="B398" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C398" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C398" s="2" t="s">
-        <v>826</v>
-      </c>
       <c r="D398" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11602,13 +11602,13 @@
         <v>634</v>
       </c>
       <c r="B399" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C399" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C399" s="2" t="s">
-        <v>828</v>
-      </c>
       <c r="D399" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11616,13 +11616,13 @@
         <v>635</v>
       </c>
       <c r="B400" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C400" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="C400" s="2" t="s">
-        <v>830</v>
-      </c>
       <c r="D400" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -11630,13 +11630,13 @@
         <v>636</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -11644,13 +11644,13 @@
         <v>637</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -11658,13 +11658,13 @@
         <v>639</v>
       </c>
       <c r="B403" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="C403" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="C403" s="3" t="s">
-        <v>834</v>
-      </c>
       <c r="D403" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -11672,27 +11672,27 @@
         <v>640</v>
       </c>
       <c r="B404" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="C404" s="3" t="s">
-        <v>836</v>
-      </c>
       <c r="D404" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A405" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="B405" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B405" s="2" t="s">
+      <c r="C405" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="C405" s="2" t="s">
+      <c r="D405" s="3" t="s">
         <v>839</v>
-      </c>
-      <c r="D405" s="3" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -11700,13 +11700,13 @@
         <v>901</v>
       </c>
       <c r="B406" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C406" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="C406" s="2" t="s">
+      <c r="D406" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="D406" s="3" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11714,13 +11714,13 @@
         <v>902</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="C407" s="2" t="s">
+      <c r="D407" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="D407" s="3" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -11728,13 +11728,13 @@
         <v>903</v>
       </c>
       <c r="B408" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C408" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="C408" s="2" t="s">
+      <c r="D408" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="D408" s="3" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -11742,55 +11742,55 @@
         <v>904</v>
       </c>
       <c r="B409" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C409" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="C409" s="2" t="s">
+      <c r="D409" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A410" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="B410" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="B410" s="2" t="s">
+      <c r="C410" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="C410" s="2" t="s">
+      <c r="D410" s="3" t="s">
         <v>855</v>
-      </c>
-      <c r="D410" s="3" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A411" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B411" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="B411" s="2" t="s">
+      <c r="C411" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="C411" s="2" t="s">
-        <v>859</v>
-      </c>
       <c r="D411" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A412" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="B412" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B412" s="2" t="s">
+      <c r="C412" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="C412" s="2" t="s">
-        <v>862</v>
-      </c>
       <c r="D412" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11798,27 +11798,27 @@
         <v>907</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A414" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="B414" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="B414" s="2" t="s">
+      <c r="C414" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="C414" s="2" t="s">
-        <v>866</v>
-      </c>
       <c r="D414" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -11826,27 +11826,27 @@
         <v>925</v>
       </c>
       <c r="B415" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C415" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="C415" s="2" t="s">
-        <v>868</v>
-      </c>
       <c r="D415" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="B416" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="B416" s="2" t="s">
+      <c r="C416" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="C416" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="D416" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11854,13 +11854,13 @@
         <v>928</v>
       </c>
       <c r="B417" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="C417" s="2" t="s">
+      <c r="D417" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="D417" s="3" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -11868,13 +11868,13 @@
         <v>930</v>
       </c>
       <c r="B418" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C418" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="C418" s="2" t="s">
-        <v>876</v>
-      </c>
       <c r="D418" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11882,13 +11882,13 @@
         <v>941</v>
       </c>
       <c r="B419" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C419" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="C419" s="2" t="s">
+      <c r="D419" s="3" t="s">
         <v>878</v>
-      </c>
-      <c r="D419" s="3" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="420" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -11896,13 +11896,13 @@
         <v>942</v>
       </c>
       <c r="B420" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C420" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="C420" s="2" t="s">
+      <c r="D420" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="D420" s="3" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11910,13 +11910,13 @@
         <v>950</v>
       </c>
       <c r="B421" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C421" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="C421" s="2" t="s">
+      <c r="D421" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="D421" s="3" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="422" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11924,55 +11924,55 @@
         <v>951</v>
       </c>
       <c r="B422" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C422" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C422" s="2" t="s">
+      <c r="D422" s="3" t="s">
         <v>887</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="B423" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="B423" s="2" t="s">
+      <c r="C423" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="C423" s="2" t="s">
+      <c r="D423" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="D423" s="3" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="B424" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="B424" s="2" t="s">
+      <c r="C424" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="C424" s="2" t="s">
-        <v>895</v>
-      </c>
       <c r="D424" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="B425" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B425" s="2" t="s">
+      <c r="C425" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="C425" s="2" t="s">
-        <v>898</v>
-      </c>
       <c r="D425" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -11980,69 +11980,69 @@
         <v>953</v>
       </c>
       <c r="B426" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="D426" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="D426" s="3" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="B427" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="B427" s="2" t="s">
-        <v>902</v>
-      </c>
       <c r="C427" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="B428" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B428" s="2" t="s">
+      <c r="C428" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="C428" s="2" t="s">
-        <v>905</v>
-      </c>
       <c r="D428" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="B429" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="B429" s="2" t="s">
+      <c r="C429" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="C429" s="2" t="s">
-        <v>908</v>
-      </c>
       <c r="D429" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="B430" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="B430" s="2" t="s">
+      <c r="C430" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="C430" s="2" t="s">
-        <v>911</v>
-      </c>
       <c r="D430" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12050,13 +12050,13 @@
         <v>955</v>
       </c>
       <c r="B431" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C431" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="C431" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="D431" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -12064,13 +12064,13 @@
         <v>956</v>
       </c>
       <c r="B432" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C432" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C432" s="2" t="s">
-        <v>915</v>
-      </c>
       <c r="D432" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12078,41 +12078,41 @@
         <v>957</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A434" s="12" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B434" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C434" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="C434" s="2" t="s">
-        <v>1052</v>
-      </c>
       <c r="D434" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A435" s="12" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B435" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C435" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="C435" s="2" t="s">
-        <v>1054</v>
-      </c>
       <c r="D435" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12120,13 +12120,13 @@
         <v>961</v>
       </c>
       <c r="B436" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C436" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="C436" s="2" t="s">
-        <v>920</v>
-      </c>
       <c r="D436" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12134,13 +12134,13 @@
         <v>962</v>
       </c>
       <c r="B437" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C437" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="C437" s="2" t="s">
-        <v>922</v>
-      </c>
       <c r="D437" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -12148,41 +12148,41 @@
         <v>964</v>
       </c>
       <c r="B438" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C438" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="C438" s="2" t="s">
-        <v>924</v>
-      </c>
       <c r="D438" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A439" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="B439" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="B439" s="2" t="s">
+      <c r="C439" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="D439" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="C439" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="D439" s="3" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A440" s="12" t="s">
+        <v>927</v>
+      </c>
+      <c r="B440" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="B440" s="2" t="s">
+      <c r="C440" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="C440" s="2" t="s">
-        <v>930</v>
-      </c>
       <c r="D440" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12190,13 +12190,13 @@
         <v>966</v>
       </c>
       <c r="B441" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="D441" s="3" t="s">
         <v>931</v>
-      </c>
-      <c r="C441" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="D441" s="3" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="442" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12204,13 +12204,13 @@
         <v>967</v>
       </c>
       <c r="B442" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="D442" s="3" t="s">
         <v>933</v>
-      </c>
-      <c r="C442" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="D442" s="3" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12218,167 +12218,167 @@
         <v>968</v>
       </c>
       <c r="B443" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="D443" s="3" t="s">
         <v>935</v>
-      </c>
-      <c r="C443" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="D443" s="3" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A444" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="B444" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="B444" s="2" t="s">
+      <c r="C444" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="C444" s="2" t="s">
+      <c r="D444" s="3" t="s">
         <v>939</v>
-      </c>
-      <c r="D444" s="3" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A445" s="12" t="s">
+        <v>940</v>
+      </c>
+      <c r="B445" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="B445" s="2" t="s">
+      <c r="C445" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="C445" s="2" t="s">
-        <v>943</v>
-      </c>
       <c r="D445" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A446" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B446" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C446" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C446" s="2" t="s">
-        <v>1056</v>
-      </c>
       <c r="D446" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A447" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B447" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C447" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="C447" s="2" t="s">
-        <v>1058</v>
-      </c>
       <c r="D447" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A448" s="12" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B448" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C448" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="C448" s="2" t="s">
-        <v>1060</v>
-      </c>
       <c r="D448" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A449" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B449" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C449" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="C449" s="2" t="s">
-        <v>1062</v>
-      </c>
       <c r="D449" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A450" s="12" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B450" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C450" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="C450" s="2" t="s">
-        <v>1064</v>
-      </c>
       <c r="D450" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A451" s="12" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B451" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C451" s="2" t="s">
-        <v>1066</v>
-      </c>
       <c r="D451" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A452" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D452" s="3" t="s">
         <v>950</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D452" s="3" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="B453" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="B453" s="2" t="s">
-        <v>953</v>
-      </c>
       <c r="C453" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A454" s="12" t="s">
+        <v>953</v>
+      </c>
+      <c r="B454" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="B454" s="2" t="s">
-        <v>955</v>
-      </c>
       <c r="C454" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -12386,13 +12386,13 @@
         <v>1102</v>
       </c>
       <c r="B455" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C455" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="C455" s="2" t="s">
-        <v>957</v>
-      </c>
       <c r="D455" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -12400,13 +12400,13 @@
         <v>1104</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -12414,13 +12414,13 @@
         <v>1105</v>
       </c>
       <c r="B457" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C457" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="C457" s="2" t="s">
-        <v>960</v>
-      </c>
       <c r="D457" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12428,13 +12428,13 @@
         <v>1200</v>
       </c>
       <c r="B458" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C458" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="C458" s="2" t="s">
+      <c r="D458" s="3" t="s">
         <v>962</v>
-      </c>
-      <c r="D458" s="3" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12442,13 +12442,13 @@
         <v>1201</v>
       </c>
       <c r="B459" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C459" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="C459" s="2" t="s">
+      <c r="D459" s="3" t="s">
         <v>965</v>
-      </c>
-      <c r="D459" s="3" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12456,13 +12456,13 @@
         <v>1202</v>
       </c>
       <c r="B460" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C460" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="C460" s="2" t="s">
+      <c r="D460" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="D460" s="3" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="461" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12470,13 +12470,13 @@
         <v>1203</v>
       </c>
       <c r="B461" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="D461" s="3" t="s">
         <v>970</v>
-      </c>
-      <c r="C461" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="D461" s="3" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="462" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12484,13 +12484,13 @@
         <v>1204</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="463" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -12498,13 +12498,13 @@
         <v>1209</v>
       </c>
       <c r="B463" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C463" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="C463" s="2" t="s">
+      <c r="D463" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="D463" s="3" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -12512,13 +12512,13 @@
         <v>1210</v>
       </c>
       <c r="B464" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="C464" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="C464" s="2" t="s">
-        <v>977</v>
-      </c>
       <c r="D464" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12526,13 +12526,13 @@
         <v>1400</v>
       </c>
       <c r="B465" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C465" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="C465" s="2" t="s">
+      <c r="D465" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="D465" s="3" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12540,13 +12540,13 @@
         <v>1401</v>
       </c>
       <c r="B466" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="C466" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="C466" s="2" t="s">
-        <v>982</v>
-      </c>
       <c r="D466" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12554,13 +12554,13 @@
         <v>1402</v>
       </c>
       <c r="B467" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="C467" s="2" t="s">
-        <v>984</v>
-      </c>
       <c r="D467" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12568,13 +12568,13 @@
         <v>1403</v>
       </c>
       <c r="B468" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C468" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="C468" s="2" t="s">
-        <v>986</v>
-      </c>
       <c r="D468" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="469" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12582,13 +12582,13 @@
         <v>1404</v>
       </c>
       <c r="B469" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C469" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="C469" s="2" t="s">
-        <v>988</v>
-      </c>
       <c r="D469" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="470" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12596,13 +12596,13 @@
         <v>1405</v>
       </c>
       <c r="B470" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="C470" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="C470" s="2" t="s">
-        <v>990</v>
-      </c>
       <c r="D470" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="471" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12610,13 +12610,13 @@
         <v>1410</v>
       </c>
       <c r="B471" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C471" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="C471" s="2" t="s">
-        <v>992</v>
-      </c>
       <c r="D471" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="472" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12624,13 +12624,13 @@
         <v>1412</v>
       </c>
       <c r="B472" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="C472" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="C472" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D472" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="473" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12638,13 +12638,13 @@
         <v>1413</v>
       </c>
       <c r="B473" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C473" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="C473" s="2" t="s">
-        <v>996</v>
-      </c>
       <c r="D473" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="474" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12652,13 +12652,13 @@
         <v>1414</v>
       </c>
       <c r="B474" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C474" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="C474" s="2" t="s">
-        <v>998</v>
-      </c>
       <c r="D474" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="475" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12666,13 +12666,13 @@
         <v>1420</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="476" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12680,13 +12680,13 @@
         <v>1421</v>
       </c>
       <c r="B476" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="C476" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="C476" s="2" t="s">
-        <v>1001</v>
-      </c>
       <c r="D476" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="477" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12694,13 +12694,13 @@
         <v>1422</v>
       </c>
       <c r="B477" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C477" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="C477" s="2" t="s">
-        <v>1003</v>
-      </c>
       <c r="D477" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="478" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12708,13 +12708,13 @@
         <v>1440</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="479" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12722,13 +12722,13 @@
         <v>1442</v>
       </c>
       <c r="B479" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C479" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="C479" s="2" t="s">
+      <c r="D479" s="3" t="s">
         <v>1006</v>
-      </c>
-      <c r="D479" s="3" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="480" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12736,13 +12736,13 @@
         <v>1450</v>
       </c>
       <c r="B480" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C480" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="C480" s="2" t="s">
-        <v>1009</v>
-      </c>
       <c r="D480" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12750,13 +12750,13 @@
         <v>1451</v>
       </c>
       <c r="B481" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C481" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="C481" s="2" t="s">
-        <v>1011</v>
-      </c>
       <c r="D481" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12764,41 +12764,41 @@
         <v>1503</v>
       </c>
       <c r="B482" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C482" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="C482" s="2" t="s">
+      <c r="D482" s="3" t="s">
         <v>1013</v>
-      </c>
-      <c r="D482" s="3" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B483" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="B483" s="2" t="s">
+      <c r="C483" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D483" s="3" t="s">
         <v>1016</v>
-      </c>
-      <c r="C483" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D483" s="3" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B484" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="B484" s="2" t="s">
+      <c r="C484" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="C484" s="2" t="s">
-        <v>1020</v>
-      </c>
       <c r="D484" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12806,13 +12806,13 @@
         <v>1505</v>
       </c>
       <c r="B485" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C485" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="C485" s="2" t="s">
+      <c r="D485" s="3" t="s">
         <v>1022</v>
-      </c>
-      <c r="D485" s="3" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12820,13 +12820,13 @@
         <v>1518</v>
       </c>
       <c r="B486" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C486" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D486" s="3" t="s">
         <v>1024</v>
-      </c>
-      <c r="C486" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D486" s="3" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -12834,13 +12834,13 @@
         <v>1520</v>
       </c>
       <c r="B487" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C487" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="C487" s="2" t="s">
+      <c r="D487" s="3" t="s">
         <v>1027</v>
-      </c>
-      <c r="D487" s="3" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -12848,13 +12848,13 @@
         <v>1521</v>
       </c>
       <c r="B488" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C488" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="C488" s="2" t="s">
+      <c r="D488" s="3" t="s">
         <v>1030</v>
-      </c>
-      <c r="D488" s="3" t="s">
-        <v>1031</v>
       </c>
     </row>
   </sheetData>

--- a/vnadditivedb.xlsx
+++ b/vnadditivedb.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="223">
   <si>
     <t>100(i)</t>
   </si>
@@ -45,6 +45,15 @@
     <t>Riboflavin, synthetic</t>
   </si>
   <si>
+    <t>101(ii)</t>
+  </si>
+  <si>
+    <t>Natri Riboflavin 5'-phosphat</t>
+  </si>
+  <si>
+    <t>Riboflavin 5'-phosphate sodium</t>
+  </si>
+  <si>
     <t>01.1.4</t>
   </si>
   <si>
@@ -156,9 +165,6 @@
     <t>Quả tươi đã xử lý bề mặt</t>
   </si>
   <si>
-    <t>4 &amp; 16</t>
-  </si>
-  <si>
     <t>04.1.2.4</t>
   </si>
   <si>
@@ -276,15 +282,9 @@
     <t>Sản phẩm thịt, thịt gia cầm và thịt thú nguyên miếng hoặc cắt nhỏ đã qua chế biến</t>
   </si>
   <si>
-    <t>16, XS96, XS97</t>
-  </si>
-  <si>
     <t>Sản phẩm thịt, thịt gia cầm và thịt thú xay nhỏ đã qua chế biến</t>
   </si>
   <si>
-    <t>16, XS88, XS89 &amp; XS98</t>
-  </si>
-  <si>
     <t>Vỏ bọc các sản phẩm thịt, có thể ăn được (VD: vỏ bọc xúc xích)</t>
   </si>
   <si>
@@ -294,18 +294,12 @@
     <t>Cá, cá phi lê và sản phẩm thủy sản đông lạnh, bao gồm cả nhuyễn thể, giáp xác, da gai</t>
   </si>
   <si>
-    <t>95, XS36, XS92, XS95, XS165, XS190, XS191, XS292, XS312, XS315</t>
-  </si>
-  <si>
     <t>09.2.2</t>
   </si>
   <si>
     <t>Cá, cá phi lê và sản phẩm thủy sản bao bột đông lạnh, bao gồm cả nhuyễn thể, giáp xác, da gai</t>
   </si>
   <si>
-    <t>16, XS166</t>
-  </si>
-  <si>
     <t>09.2.3</t>
   </si>
   <si>
@@ -336,9 +330,6 @@
     <t>Thủy sản và sản phẩm thủy sản hun khói, sấy khô, lên men hoặc ướp muối, bao gồm cả nhuyễn thể, giáp xác, da gai</t>
   </si>
   <si>
-    <t>22, XS167, XS189, XS222, XS236, XS244, XS311</t>
-  </si>
-  <si>
     <t>09.3.1</t>
   </si>
   <si>
@@ -369,9 +360,6 @@
     <t>Thủy sản và sản phẩm thủy sản lên men hoặc đóng hộp, kể cả nhuyễn thể, giáp xác, da gai đóng hộp được bảo quản hoàn toàn</t>
   </si>
   <si>
-    <t>95, XS3, XS37, XS70, XS90, XS94 &amp; XS119</t>
-  </si>
-  <si>
     <t>Trứng tươi</t>
   </si>
   <si>
@@ -556,14 +544,151 @@
   </si>
   <si>
     <t>ins</t>
+  </si>
+  <si>
+    <t>Đối với các sản phẩm được quy định tại tiêu chuẩn Codex stan 92-1981 và Codex stan 95-1981: sử dụng các phụ gia INS 220, INS 221, INS 222, INS 223, INS 224, INS 225 làm chất bảo quản với mức sử dụng tối đa 100 mg/kg phần ăn được của sản phẩm thô hoặc 30 mg/kg trong phần ăn được của sản phẩm đã chế biến</t>
+  </si>
+  <si>
+    <t>Chỉ sử dụng sản phẩm cá xay nhuyễn xông khói</t>
+  </si>
+  <si>
+    <t>Chỉ sử dụng phụ gia thực phẩm INS101(i) cho sản phẩm quy định trong tiêu chuẩn Codex stan 117-1981</t>
+  </si>
+  <si>
+    <t>XS92</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 92-1981</t>
+  </si>
+  <si>
+    <t>XS95</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 95-1981</t>
+  </si>
+  <si>
+    <t>XS165</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 165-1989</t>
+  </si>
+  <si>
+    <t>XS166</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 166-1989</t>
+  </si>
+  <si>
+    <t>XS189</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 189-1993</t>
+  </si>
+  <si>
+    <t>XS190</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 190-1995</t>
+  </si>
+  <si>
+    <t>XS191</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 191-1995</t>
+  </si>
+  <si>
+    <t>XS222</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 222-2001</t>
+  </si>
+  <si>
+    <t>XS236</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 236-2003</t>
+  </si>
+  <si>
+    <t>XS292</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 292-2008</t>
+  </si>
+  <si>
+    <t>XS311</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 311-2013</t>
+  </si>
+  <si>
+    <t>XS312</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 312-2013</t>
+  </si>
+  <si>
+    <t>XS315</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 315-2014</t>
+  </si>
+  <si>
+    <t>XS167</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 167-1989</t>
+  </si>
+  <si>
+    <t>XS244</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 244-2004</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 291-2010</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 302-2011</t>
+  </si>
+  <si>
+    <t>XS94</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 94-1981</t>
+  </si>
+  <si>
+    <t>XS3</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 3-1981</t>
+  </si>
+  <si>
+    <t>XS37</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 37-1991</t>
+  </si>
+  <si>
+    <t>XS70</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 70-1981</t>
+  </si>
+  <si>
+    <t>XS90</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 90-1981</t>
+  </si>
+  <si>
+    <t>XS119</t>
+  </si>
+  <si>
+    <t>Không bao gồm các sản phẩm quy định trong tiêu chuẩn Codex stan 119-1981</t>
   </si>
   <si>
     <t xml:space="preserve">Thông tư 24/2019/TT-BYT
 Phụ lục 2A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông tư 24/2019/TT-BYT
-</t>
   </si>
 </sst>
 </file>
@@ -599,7 +724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -607,11 +732,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -667,6 +872,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -694,6 +905,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -975,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
@@ -985,7 +1244,7 @@
     <col min="5" max="5" width="11.28515625" style="14" customWidth="1"/>
     <col min="6" max="6" width="38.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="3"/>
+    <col min="8" max="8" width="31.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="46" style="3" customWidth="1"/>
     <col min="10" max="10" width="32" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="3"/>
@@ -993,70 +1252,58 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="16">
-        <v>150</v>
-      </c>
-      <c r="H2" s="17">
-        <v>52</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="D2" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -1069,26 +1316,26 @@
         <v>2</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3" s="16">
         <v>150</v>
       </c>
       <c r="H3" s="17">
-        <v>402</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="15" t="s">
@@ -1100,78 +1347,76 @@
       <c r="D4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="16">
+        <v>150</v>
+      </c>
+      <c r="H4" s="17">
+        <v>402</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="43">
         <v>12.5</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="16">
+      <c r="F5" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="45">
         <v>50</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H5" s="44">
         <v>99</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="I5" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="12">
-        <v>300</v>
-      </c>
-      <c r="H6" s="5">
-        <v>52</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>179</v>
-      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -1183,21 +1428,17 @@
       <c r="C7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="12">
-        <v>300</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1207,45 +1448,57 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="12">
+        <v>300</v>
+      </c>
+      <c r="H8" s="5">
+        <v>52</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="12">
-        <v>300</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="F9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="12">
         <v>300</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
@@ -1255,21 +1508,25 @@
       <c r="C10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="22">
+      <c r="D10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="12">
         <v>300</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
@@ -1279,21 +1536,25 @@
       <c r="C11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="20" t="s">
+      <c r="D11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="22">
+      <c r="G11" s="24">
         <v>300</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>5</v>
       </c>
@@ -1303,21 +1564,25 @@
       <c r="C12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="20" t="s">
+      <c r="D12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <v>300</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
@@ -1327,21 +1592,25 @@
       <c r="C13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="20" t="s">
+      <c r="D13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="22">
+      <c r="G13" s="24">
         <v>300</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="J13" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
@@ -1351,19 +1620,23 @@
       <c r="C14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="23" t="s">
+      <c r="D14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="24">
         <v>300</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="J14" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -1375,45 +1648,53 @@
       <c r="C15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="G15" s="24">
+        <v>300</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="24">
-        <v>300</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>40</v>
-      </c>
       <c r="G16" s="24">
         <v>300</v>
       </c>
-      <c r="H16" s="25"/>
+      <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="J16" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>5</v>
       </c>
@@ -1423,21 +1704,25 @@
       <c r="C17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17" s="21" t="s">
+      <c r="D17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="24">
-        <v>300</v>
-      </c>
-      <c r="H17" s="25"/>
+      <c r="F17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="26">
+        <v>300</v>
+      </c>
+      <c r="H17" s="27"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="J17" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>5</v>
       </c>
@@ -1447,20 +1732,25 @@
       <c r="C18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="24">
-        <v>500</v>
-      </c>
-      <c r="H18" s="25"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="26">
+        <v>300</v>
+      </c>
+      <c r="H18" s="27"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>5</v>
       </c>
@@ -1470,20 +1760,23 @@
       <c r="C19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="21" t="s">
+      <c r="D19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="24">
-        <v>300</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="G19" s="26">
+        <v>300</v>
+      </c>
+      <c r="H19" s="27"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -1495,16 +1788,23 @@
       <c r="C20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25">
-        <v>4</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="J20" s="2"/>
+      <c r="D20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="26">
+        <v>500</v>
+      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -1516,114 +1816,149 @@
       <c r="C21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25">
+      <c r="D21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="26">
+        <v>300</v>
+      </c>
+      <c r="H21" s="27">
+        <v>4</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="26">
+        <v>300</v>
+      </c>
+      <c r="H22" s="27">
         <v>16</v>
       </c>
-      <c r="I21" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="24">
-        <v>300</v>
-      </c>
-      <c r="H22" s="25">
+      <c r="I22" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="26">
+        <v>300</v>
+      </c>
+      <c r="H23" s="27">
         <v>267</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="24">
+      <c r="I23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="26">
         <v>200</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="H24" s="27"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="26">
         <v>500</v>
       </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="24">
-        <v>300</v>
-      </c>
-      <c r="H25" s="25"/>
+      <c r="H25" s="27"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="J25" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>5</v>
       </c>
@@ -1633,22 +1968,23 @@
       <c r="C26" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="24">
-        <v>300</v>
-      </c>
-      <c r="H26" s="25">
-        <v>182</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="J26" s="2"/>
+      <c r="G26" s="26">
+        <v>300</v>
+      </c>
+      <c r="H26" s="27"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
@@ -1660,20 +1996,29 @@
       <c r="C27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="D27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="24">
-        <v>300</v>
-      </c>
-      <c r="H27" s="25"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G27" s="26">
+        <v>300</v>
+      </c>
+      <c r="H27" s="27">
+        <v>182</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>5</v>
       </c>
@@ -1683,43 +2028,53 @@
       <c r="C28" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="D28" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="26">
+        <v>300</v>
+      </c>
+      <c r="H28" s="27"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="26">
         <v>500</v>
       </c>
-      <c r="H28" s="25"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" s="24">
-        <v>300</v>
-      </c>
-      <c r="H29" s="25"/>
+      <c r="H29" s="27"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="J29" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>5</v>
       </c>
@@ -1729,22 +2084,25 @@
       <c r="C30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="D30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="24">
-        <v>300</v>
-      </c>
-      <c r="H30" s="25" t="s">
-        <v>45</v>
-      </c>
+      <c r="G30" s="26">
+        <v>300</v>
+      </c>
+      <c r="H30" s="27"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="J30" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>5</v>
       </c>
@@ -1754,18 +2112,29 @@
       <c r="C31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24">
+      <c r="D31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="26">
+        <v>300</v>
+      </c>
+      <c r="H31" s="26">
         <v>4</v>
       </c>
-      <c r="I31" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I31" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>5</v>
       </c>
@@ -1775,16 +2144,27 @@
       <c r="C32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24">
+      <c r="D32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" s="26">
+        <v>300</v>
+      </c>
+      <c r="H32" s="26">
         <v>16</v>
       </c>
-      <c r="I32" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J32" s="2"/>
+      <c r="I32" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="33" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
@@ -1796,18 +2176,23 @@
       <c r="C33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G33" s="24">
+      <c r="D33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="26">
         <v>500</v>
       </c>
-      <c r="H33" s="25"/>
+      <c r="H33" s="27"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="J33" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
@@ -1819,22 +2204,27 @@
       <c r="C34" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="24">
-        <v>300</v>
-      </c>
-      <c r="H34" s="25">
+      <c r="D34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="26">
+        <v>300</v>
+      </c>
+      <c r="H34" s="27">
         <v>92</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J34" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
@@ -1846,18 +2236,23 @@
       <c r="C35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G35" s="24">
+      <c r="D35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="26">
         <v>500</v>
       </c>
-      <c r="H35" s="25"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+      <c r="J35" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
@@ -1869,18 +2264,23 @@
       <c r="C36" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G36" s="24">
+      <c r="D36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="26">
         <v>1000</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="27"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
+      <c r="J36" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
@@ -1892,24 +2292,29 @@
       <c r="C37" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="24">
+      <c r="D37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="26">
         <v>1000</v>
       </c>
-      <c r="H37" s="25" t="s">
-        <v>73</v>
+      <c r="H37" s="27" t="s">
+        <v>75</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>5</v>
       </c>
@@ -1919,18 +2324,23 @@
       <c r="C38" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G38" s="24">
+      <c r="D38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="26">
         <v>1000</v>
       </c>
-      <c r="H38" s="25"/>
+      <c r="H38" s="27"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
+      <c r="J38" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="39" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
@@ -1942,18 +2352,23 @@
       <c r="C39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G39" s="24">
+      <c r="D39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="26">
         <v>1000</v>
       </c>
-      <c r="H39" s="25"/>
+      <c r="H39" s="27"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
+      <c r="J39" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -1965,18 +2380,23 @@
       <c r="C40" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="24">
-        <v>300</v>
-      </c>
-      <c r="H40" s="25"/>
+      <c r="D40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G40" s="26">
+        <v>300</v>
+      </c>
+      <c r="H40" s="27"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
+      <c r="J40" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
@@ -1988,22 +2408,27 @@
       <c r="C41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="24">
-        <v>300</v>
-      </c>
-      <c r="H41" s="25">
+      <c r="D41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="26">
+        <v>300</v>
+      </c>
+      <c r="H41" s="27">
         <v>153</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J41" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
@@ -2015,18 +2440,23 @@
       <c r="C42" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="G42" s="24">
-        <v>300</v>
-      </c>
-      <c r="H42" s="25"/>
+      <c r="D42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="26">
+        <v>300</v>
+      </c>
+      <c r="H42" s="27"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+      <c r="J42" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
@@ -2038,20 +2468,25 @@
       <c r="C43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G43" s="24">
-        <v>300</v>
-      </c>
-      <c r="H43" s="25"/>
+      <c r="D43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="26">
+        <v>300</v>
+      </c>
+      <c r="H43" s="27"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>5</v>
       </c>
@@ -2061,18 +2496,23 @@
       <c r="C44" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="24">
+      <c r="D44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" s="26">
         <v>50</v>
       </c>
-      <c r="H44" s="25"/>
+      <c r="H44" s="27"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
+      <c r="J44" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
@@ -2084,18 +2524,23 @@
       <c r="C45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="G45" s="24">
-        <v>300</v>
-      </c>
-      <c r="H45" s="25"/>
+      <c r="D45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" s="26">
+        <v>300</v>
+      </c>
+      <c r="H45" s="27"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
+      <c r="J45" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
@@ -2107,22 +2552,29 @@
       <c r="C46" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G46" s="24">
+      <c r="D46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G46" s="26">
         <v>1000</v>
       </c>
-      <c r="H46" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="H46" s="27">
+        <v>16</v>
+      </c>
+      <c r="I46" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>5</v>
       </c>
@@ -2132,18 +2584,29 @@
       <c r="C47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="20"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="25">
-        <v>16</v>
-      </c>
-      <c r="I47" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G47" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>5</v>
       </c>
@@ -2153,16 +2616,27 @@
       <c r="C48" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="20"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="25" t="s">
-        <v>170</v>
+      <c r="D48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G48" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J48" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
@@ -2174,18 +2648,29 @@
       <c r="C49" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="D49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H49" s="27">
+        <v>16</v>
+      </c>
+      <c r="I49" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>5</v>
       </c>
@@ -2195,20 +2680,27 @@
       <c r="C50" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G50" s="24">
+      <c r="D50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" s="26">
         <v>1000</v>
       </c>
-      <c r="H50" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
+      <c r="H50" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
@@ -2220,16 +2712,27 @@
       <c r="C51" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="20"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="25">
-        <v>16</v>
-      </c>
-      <c r="I51" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J51" s="2"/>
+      <c r="D51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
@@ -2241,16 +2744,27 @@
       <c r="C52" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="20"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="25" t="s">
-        <v>166</v>
+      <c r="D52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G52" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="27" t="s">
+        <v>170</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J52" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
@@ -2262,18 +2776,29 @@
       <c r="C53" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="20"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H53" s="27">
+        <v>16</v>
+      </c>
+      <c r="I53" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>5</v>
       </c>
@@ -2283,18 +2808,29 @@
       <c r="C54" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="20"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="25" t="s">
-        <v>174</v>
+      <c r="D54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H54" s="27">
+        <v>95</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>5</v>
       </c>
@@ -2304,24 +2840,29 @@
       <c r="C55" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G55" s="24">
+      <c r="D55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" s="26">
         <v>1000</v>
       </c>
-      <c r="H55" s="25">
-        <v>16</v>
-      </c>
-      <c r="I55" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="H55" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>5</v>
       </c>
@@ -2331,22 +2872,29 @@
       <c r="C56" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="D56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F56" s="21" t="s">
+      <c r="F56" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G56" s="24">
+      <c r="G56" s="26">
         <v>1000</v>
       </c>
-      <c r="H56" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="H56" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>5</v>
       </c>
@@ -2356,18 +2904,29 @@
       <c r="C57" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E57" s="20"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="25">
-        <v>95</v>
+      <c r="D57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="27" t="s">
+        <v>180</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J57" s="2"/>
-    </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>5</v>
       </c>
@@ -2377,16 +2936,27 @@
       <c r="C58" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E58" s="20"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="25" t="s">
-        <v>164</v>
+      <c r="D58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="27" t="s">
+        <v>182</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J58" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
@@ -2398,20 +2968,27 @@
       <c r="C59" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E59" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="G59" s="24">
-        <v>300</v>
-      </c>
-      <c r="H59" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
+      <c r="D59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
@@ -2423,22 +3000,29 @@
       <c r="C60" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E60" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G60" s="24">
-        <v>300</v>
-      </c>
-      <c r="H60" s="25">
-        <v>16</v>
-      </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H60" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>5</v>
       </c>
@@ -2448,22 +3032,29 @@
       <c r="C61" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G61" s="24">
-        <v>300</v>
-      </c>
-      <c r="H61" s="25">
-        <v>95</v>
-      </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>5</v>
       </c>
@@ -2473,18 +3064,27 @@
       <c r="C62" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F62" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G62" s="24">
-        <v>300</v>
-      </c>
-      <c r="H62" s="25"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
+      <c r="D62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
@@ -2496,45 +3096,59 @@
       <c r="C63" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="G63" s="24">
-        <v>300</v>
-      </c>
-      <c r="H63" s="25">
+      <c r="D63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" s="26">
+        <v>1000</v>
+      </c>
+      <c r="H63" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="G64" s="26">
+        <v>300</v>
+      </c>
+      <c r="H64" s="26">
         <v>16</v>
       </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-    </row>
-    <row r="64" spans="1:10" ht="105" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G64" s="24">
-        <v>300</v>
-      </c>
-      <c r="H64" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
+      <c r="I64" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="65" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
@@ -2546,20 +3160,27 @@
       <c r="C65" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="G65" s="24">
-        <v>300</v>
-      </c>
-      <c r="H65" s="25">
-        <v>16</v>
-      </c>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
+      <c r="D65" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="G65" s="26">
+        <v>300</v>
+      </c>
+      <c r="H65" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
@@ -2571,22 +3192,29 @@
       <c r="C66" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="G66" s="24">
-        <v>300</v>
-      </c>
-      <c r="H66" s="25">
+      <c r="D66" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G66" s="26">
+        <v>300</v>
+      </c>
+      <c r="H66" s="26">
         <v>16</v>
       </c>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I66" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>5</v>
       </c>
@@ -2596,22 +3224,29 @@
       <c r="C67" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E67" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="G67" s="24">
-        <v>300</v>
-      </c>
-      <c r="H67" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="D67" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" s="26">
+        <v>300</v>
+      </c>
+      <c r="H67" s="26">
+        <v>19</v>
+      </c>
+      <c r="I67" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>5</v>
       </c>
@@ -2621,20 +3256,25 @@
       <c r="C68" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="24">
-        <v>300</v>
-      </c>
-      <c r="H68" s="25"/>
+      <c r="D68" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G68" s="26">
+        <v>300</v>
+      </c>
+      <c r="H68" s="27"/>
       <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="J68" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>5</v>
       </c>
@@ -2644,22 +3284,29 @@
       <c r="C69" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="G69" s="24">
-        <v>500</v>
-      </c>
-      <c r="H69" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D69" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="G69" s="26">
+        <v>300</v>
+      </c>
+      <c r="H69" s="26">
+        <v>16</v>
+      </c>
+      <c r="I69" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>5</v>
       </c>
@@ -2669,22 +3316,29 @@
       <c r="C70" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="20">
-        <v>10.1</v>
-      </c>
-      <c r="F70" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="G70" s="24">
-        <v>300</v>
-      </c>
-      <c r="H70" s="25">
-        <v>4</v>
-      </c>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D70" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" s="26">
+        <v>300</v>
+      </c>
+      <c r="H70" s="26">
+        <v>22</v>
+      </c>
+      <c r="I70" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>5</v>
       </c>
@@ -2694,20 +3348,29 @@
       <c r="C71" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="20">
-        <v>10.4</v>
-      </c>
-      <c r="F71" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="G71" s="24">
-        <v>300</v>
-      </c>
-      <c r="H71" s="25"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="D71" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G71" s="26">
+        <v>300</v>
+      </c>
+      <c r="H71" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>5</v>
       </c>
@@ -2717,20 +3380,29 @@
       <c r="C72" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="20">
-        <v>11.3</v>
-      </c>
-      <c r="F72" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="G72" s="24">
-        <v>300</v>
-      </c>
-      <c r="H72" s="25"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D72" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G72" s="26">
+        <v>300</v>
+      </c>
+      <c r="H72" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>5</v>
       </c>
@@ -2740,20 +3412,29 @@
       <c r="C73" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="20">
-        <v>11.4</v>
-      </c>
-      <c r="F73" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="G73" s="24">
-        <v>300</v>
-      </c>
-      <c r="H73" s="25"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D73" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G73" s="26">
+        <v>300</v>
+      </c>
+      <c r="H73" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>5</v>
       </c>
@@ -2763,20 +3444,29 @@
       <c r="C74" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F74" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G74" s="24">
-        <v>350</v>
-      </c>
-      <c r="H74" s="25"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D74" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G74" s="26">
+        <v>300</v>
+      </c>
+      <c r="H74" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J74" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>5</v>
       </c>
@@ -2786,20 +3476,29 @@
       <c r="C75" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="20">
-        <v>12.4</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="G75" s="24">
-        <v>300</v>
-      </c>
-      <c r="H75" s="25"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D75" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G75" s="26">
+        <v>300</v>
+      </c>
+      <c r="H75" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>5</v>
       </c>
@@ -2809,22 +3508,29 @@
       <c r="C76" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="20">
-        <v>12.5</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="24">
-        <v>200</v>
-      </c>
-      <c r="H76" s="25">
-        <v>344</v>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D76" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G76" s="26">
+        <v>300</v>
+      </c>
+      <c r="H76" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>5</v>
       </c>
@@ -2834,22 +3540,29 @@
       <c r="C77" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="20">
-        <v>12.6</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="G77" s="24">
-        <v>350</v>
-      </c>
-      <c r="H77" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="D77" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F77" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G77" s="26">
+        <v>300</v>
+      </c>
+      <c r="H77" s="27">
+        <v>16</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>5</v>
       </c>
@@ -2859,18 +3572,27 @@
       <c r="C78" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="20">
-        <v>12.7</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G78" s="24">
-        <v>300</v>
-      </c>
-      <c r="H78" s="25"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
+      <c r="D78" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F78" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G78" s="26">
+        <v>300</v>
+      </c>
+      <c r="H78" s="27">
+        <v>16</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
@@ -2882,20 +3604,29 @@
       <c r="C79" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="G79" s="24">
-        <v>30</v>
-      </c>
-      <c r="H79" s="25"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="D79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G79" s="26">
+        <v>300</v>
+      </c>
+      <c r="H79" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>5</v>
       </c>
@@ -2905,20 +3636,25 @@
       <c r="C80" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="20">
-        <v>13.3</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G80" s="24">
-        <v>300</v>
-      </c>
-      <c r="H80" s="25"/>
+      <c r="D80" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G80" s="26">
+        <v>300</v>
+      </c>
+      <c r="H80" s="27"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J80" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>5</v>
       </c>
@@ -2928,18 +3664,27 @@
       <c r="C81" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="20">
-        <v>13.4</v>
-      </c>
-      <c r="F81" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="G81" s="24">
-        <v>300</v>
-      </c>
-      <c r="H81" s="25"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
+      <c r="D81" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F81" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G81" s="26">
+        <v>500</v>
+      </c>
+      <c r="H81" s="27">
+        <v>95</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="82" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
@@ -2951,20 +3696,29 @@
       <c r="C82" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="20">
-        <v>13.5</v>
-      </c>
-      <c r="F82" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G82" s="24">
-        <v>300</v>
-      </c>
-      <c r="H82" s="25"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D82" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F82" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G82" s="26">
+        <v>500</v>
+      </c>
+      <c r="H82" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>5</v>
       </c>
@@ -2974,20 +3728,27 @@
       <c r="C83" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="20">
-        <v>13.6</v>
-      </c>
-      <c r="F83" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="G83" s="24">
-        <v>300</v>
-      </c>
-      <c r="H83" s="25"/>
-      <c r="I83" s="2"/>
+      <c r="D83" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F83" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G83" s="26">
+        <v>500</v>
+      </c>
+      <c r="H83" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="J83" s="2"/>
     </row>
-    <row r="84" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>5</v>
       </c>
@@ -2997,20 +3758,29 @@
       <c r="C84" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F84" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G84" s="24">
-        <v>50</v>
-      </c>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D84" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G84" s="26">
+        <v>500</v>
+      </c>
+      <c r="H84" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>5</v>
       </c>
@@ -3020,20 +3790,29 @@
       <c r="C85" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="F85" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="G85" s="24">
-        <v>300</v>
-      </c>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D85" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F85" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G85" s="26">
+        <v>500</v>
+      </c>
+      <c r="H85" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>5</v>
       </c>
@@ -3043,20 +3822,29 @@
       <c r="C86" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="F86" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="G86" s="24">
-        <v>300</v>
-      </c>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="D86" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F86" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" s="26">
+        <v>500</v>
+      </c>
+      <c r="H86" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J86" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>5</v>
       </c>
@@ -3066,18 +3854,27 @@
       <c r="C87" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F87" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="G87" s="24">
-        <v>100</v>
-      </c>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
+      <c r="D87" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F87" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G87" s="26">
+        <v>500</v>
+      </c>
+      <c r="H87" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="88" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
@@ -3089,41 +3886,581 @@
       <c r="C88" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="20">
+      <c r="D88" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="22">
+        <v>10.1</v>
+      </c>
+      <c r="F88" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="G88" s="26">
+        <v>300</v>
+      </c>
+      <c r="H88" s="27">
+        <v>4</v>
+      </c>
+      <c r="I88" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="22">
+        <v>10.4</v>
+      </c>
+      <c r="F89" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G89" s="26">
+        <v>300</v>
+      </c>
+      <c r="H89" s="27"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="22">
+        <v>11.3</v>
+      </c>
+      <c r="F90" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G90" s="26">
+        <v>300</v>
+      </c>
+      <c r="H90" s="27"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="22">
+        <v>11.4</v>
+      </c>
+      <c r="F91" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" s="26">
+        <v>300</v>
+      </c>
+      <c r="H91" s="27"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G92" s="26">
+        <v>350</v>
+      </c>
+      <c r="H92" s="27"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="22">
+        <v>12.4</v>
+      </c>
+      <c r="F93" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="G93" s="26">
+        <v>300</v>
+      </c>
+      <c r="H93" s="27"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="22">
+        <v>12.5</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" s="26">
+        <v>200</v>
+      </c>
+      <c r="H94" s="27">
+        <v>344</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E95" s="22">
+        <v>12.6</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G95" s="26">
+        <v>350</v>
+      </c>
+      <c r="H95" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="22">
+        <v>12.7</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G96" s="26">
+        <v>300</v>
+      </c>
+      <c r="H96" s="27"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E97" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F97" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G97" s="26">
+        <v>30</v>
+      </c>
+      <c r="H97" s="27"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E98" s="22">
+        <v>13.3</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G98" s="26">
+        <v>300</v>
+      </c>
+      <c r="H98" s="27"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99" s="22">
+        <v>13.4</v>
+      </c>
+      <c r="F99" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" s="26">
+        <v>300</v>
+      </c>
+      <c r="H99" s="27"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G100" s="26">
+        <v>300</v>
+      </c>
+      <c r="H100" s="27"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E101" s="22">
+        <v>13.6</v>
+      </c>
+      <c r="F101" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="G101" s="26">
+        <v>300</v>
+      </c>
+      <c r="H101" s="27"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E102" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F102" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G102" s="26">
+        <v>50</v>
+      </c>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F103" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G103" s="26">
+        <v>300</v>
+      </c>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E104" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F104" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G104" s="26">
+        <v>300</v>
+      </c>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E105" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F105" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G105" s="26">
+        <v>100</v>
+      </c>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E106" s="22">
         <v>15.1</v>
       </c>
-      <c r="F88" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="G88" s="24">
+      <c r="F106" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G106" s="26">
         <v>1000</v>
       </c>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" s="20">
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="22">
         <v>15.2</v>
       </c>
-      <c r="F89" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G89" s="24">
+      <c r="F107" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="G107" s="26">
         <v>1000</v>
       </c>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/vnadditivedb.xlsx
+++ b/vnadditivedb.xlsx
@@ -2407,9 +2407,6 @@
     <t>Mixes for soups and broths</t>
   </si>
   <si>
-    <t>Excluding products conforming CODEX STAN 117-1981.</t>
-  </si>
-  <si>
     <t>14.1.4.1</t>
   </si>
   <si>
@@ -2483,6 +2480,9 @@
   </si>
   <si>
     <t xml:space="preserve"> XS117</t>
+  </si>
+  <si>
+    <t>Excluding products conforming to CODEX STAN 117-1981.</t>
   </si>
 </sst>
 </file>
@@ -85912,7 +85912,7 @@
         <v>739</v>
       </c>
       <c r="M1906" s="55" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="N1906" s="62" t="s">
         <v>419</v>
@@ -85979,10 +85979,10 @@
         <v>411</v>
       </c>
       <c r="F1908" s="73" t="s">
+        <v>740</v>
+      </c>
+      <c r="G1908" s="74" t="s">
         <v>741</v>
-      </c>
-      <c r="G1908" s="74" t="s">
-        <v>742</v>
       </c>
       <c r="H1908" s="75">
         <v>5</v>
@@ -85993,7 +85993,7 @@
         <v>296</v>
       </c>
       <c r="L1908" s="51" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="N1908" s="62" t="s">
         <v>419</v>
@@ -86016,10 +86016,10 @@
         <v>411</v>
       </c>
       <c r="F1909" s="73" t="s">
+        <v>743</v>
+      </c>
+      <c r="G1909" s="74" t="s">
         <v>744</v>
-      </c>
-      <c r="G1909" s="74" t="s">
-        <v>745</v>
       </c>
       <c r="H1909" s="75">
         <v>5</v>
@@ -86030,7 +86030,7 @@
         <v>296</v>
       </c>
       <c r="L1909" s="33" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="N1909" s="62" t="s">
         <v>419</v>
@@ -86053,10 +86053,10 @@
         <v>411</v>
       </c>
       <c r="F1910" s="73" t="s">
+        <v>746</v>
+      </c>
+      <c r="G1910" s="74" t="s">
         <v>747</v>
-      </c>
-      <c r="G1910" s="74" t="s">
-        <v>748</v>
       </c>
       <c r="H1910" s="75">
         <v>5</v>
@@ -86071,7 +86071,7 @@
         <v>296</v>
       </c>
       <c r="L1910" s="33" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="M1910" s="40" t="s">
         <v>593</v>
@@ -86193,13 +86193,13 @@
     </row>
     <row r="1914" spans="1:14" ht="45">
       <c r="A1914" s="15" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1914" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="B1914" s="15" t="s">
+      <c r="C1914" s="15" t="s">
         <v>751</v>
-      </c>
-      <c r="C1914" s="15" t="s">
-        <v>752</v>
       </c>
       <c r="D1914" s="15" t="s">
         <v>2</v>
@@ -86237,13 +86237,13 @@
     </row>
     <row r="1915" spans="1:14" ht="45">
       <c r="A1915" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1915" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="B1915" s="12" t="s">
+      <c r="C1915" s="12" t="s">
         <v>751</v>
-      </c>
-      <c r="C1915" s="12" t="s">
-        <v>752</v>
       </c>
       <c r="D1915" s="12" t="s">
         <v>2</v>
@@ -86264,7 +86264,7 @@
         <v>400</v>
       </c>
       <c r="J1915" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="K1915" s="16" t="s">
         <v>296</v>
@@ -86284,10 +86284,10 @@
         <v>162</v>
       </c>
       <c r="B1916" s="91" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C1916" s="91" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D1916" s="92" t="s">
         <v>2</v>
@@ -86307,13 +86307,13 @@
     </row>
     <row r="1917" spans="1:14" ht="45">
       <c r="A1917" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1917" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1917" s="33" t="s">
+      <c r="C1917" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1917" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1917" s="34" t="s">
         <v>2</v>
@@ -86351,13 +86351,13 @@
     </row>
     <row r="1918" spans="1:14" ht="45">
       <c r="A1918" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1918" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1918" s="33" t="s">
+      <c r="C1918" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1918" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1918" s="34" t="s">
         <v>2</v>
@@ -86378,7 +86378,7 @@
         <v>181</v>
       </c>
       <c r="J1918" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1918" s="16" t="s">
         <v>296</v>
@@ -86387,7 +86387,7 @@
         <v>418</v>
       </c>
       <c r="M1918" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1918" s="23" t="s">
         <v>419</v>
@@ -86395,13 +86395,13 @@
     </row>
     <row r="1919" spans="1:14" ht="60">
       <c r="A1919" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1919" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1919" s="33" t="s">
+      <c r="C1919" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1919" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1919" s="34" t="s">
         <v>2</v>
@@ -86439,13 +86439,13 @@
     </row>
     <row r="1920" spans="1:14" ht="45">
       <c r="A1920" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1920" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1920" s="33" t="s">
+      <c r="C1920" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1920" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1920" s="34" t="s">
         <v>2</v>
@@ -86466,7 +86466,7 @@
         <v>181</v>
       </c>
       <c r="J1920" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1920" s="16" t="s">
         <v>296</v>
@@ -86475,7 +86475,7 @@
         <v>460</v>
       </c>
       <c r="M1920" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1920" s="23" t="s">
         <v>419</v>
@@ -86483,13 +86483,13 @@
     </row>
     <row r="1921" spans="1:14" ht="45">
       <c r="A1921" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1921" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1921" s="33" t="s">
+      <c r="C1921" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1921" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1921" s="34" t="s">
         <v>2</v>
@@ -86527,13 +86527,13 @@
     </row>
     <row r="1922" spans="1:14" ht="45">
       <c r="A1922" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1922" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1922" s="33" t="s">
+      <c r="C1922" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1922" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1922" s="34" t="s">
         <v>2</v>
@@ -86554,7 +86554,7 @@
         <v>181</v>
       </c>
       <c r="J1922" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1922" s="16" t="s">
         <v>296</v>
@@ -86563,7 +86563,7 @@
         <v>422</v>
       </c>
       <c r="M1922" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1922" s="23" t="s">
         <v>419</v>
@@ -86571,13 +86571,13 @@
     </row>
     <row r="1923" spans="1:14" ht="45">
       <c r="A1923" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1923" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1923" s="33" t="s">
+      <c r="C1923" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1923" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1923" s="34" t="s">
         <v>2</v>
@@ -86615,13 +86615,13 @@
     </row>
     <row r="1924" spans="1:14" ht="45">
       <c r="A1924" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1924" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1924" s="33" t="s">
+      <c r="C1924" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1924" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1924" s="34" t="s">
         <v>2</v>
@@ -86659,13 +86659,13 @@
     </row>
     <row r="1925" spans="1:14" ht="45">
       <c r="A1925" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1925" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1925" s="33" t="s">
+      <c r="C1925" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1925" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1925" s="34" t="s">
         <v>2</v>
@@ -86697,13 +86697,13 @@
     </row>
     <row r="1926" spans="1:14" ht="45">
       <c r="A1926" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1926" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1926" s="33" t="s">
+      <c r="C1926" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1926" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1926" s="34" t="s">
         <v>2</v>
@@ -86735,13 +86735,13 @@
     </row>
     <row r="1927" spans="1:14" ht="45">
       <c r="A1927" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1927" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1927" s="33" t="s">
+      <c r="C1927" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1927" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1927" s="34" t="s">
         <v>2</v>
@@ -86773,13 +86773,13 @@
     </row>
     <row r="1928" spans="1:14" ht="45">
       <c r="A1928" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1928" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1928" s="33" t="s">
+      <c r="C1928" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1928" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1928" s="34" t="s">
         <v>2</v>
@@ -86800,7 +86800,7 @@
         <v>181</v>
       </c>
       <c r="J1928" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1928" s="16" t="s">
         <v>296</v>
@@ -86809,7 +86809,7 @@
         <v>428</v>
       </c>
       <c r="M1928" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1928" s="23" t="s">
         <v>419</v>
@@ -86817,13 +86817,13 @@
     </row>
     <row r="1929" spans="1:14" ht="45">
       <c r="A1929" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1929" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1929" s="33" t="s">
+      <c r="C1929" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1929" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1929" s="34" t="s">
         <v>2</v>
@@ -86844,7 +86844,7 @@
         <v>181</v>
       </c>
       <c r="J1929" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1929" s="16" t="s">
         <v>296</v>
@@ -86853,7 +86853,7 @@
         <v>431</v>
       </c>
       <c r="M1929" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1929" s="23" t="s">
         <v>419</v>
@@ -86861,13 +86861,13 @@
     </row>
     <row r="1930" spans="1:14" ht="45">
       <c r="A1930" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1930" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1930" s="33" t="s">
+      <c r="C1930" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1930" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1930" s="34" t="s">
         <v>2</v>
@@ -86888,7 +86888,7 @@
         <v>181</v>
       </c>
       <c r="J1930" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1930" s="16" t="s">
         <v>296</v>
@@ -86897,7 +86897,7 @@
         <v>432</v>
       </c>
       <c r="M1930" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1930" s="23" t="s">
         <v>419</v>
@@ -86905,13 +86905,13 @@
     </row>
     <row r="1931" spans="1:14" ht="45">
       <c r="A1931" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1931" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1931" s="33" t="s">
+      <c r="C1931" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1931" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1931" s="34" t="s">
         <v>2</v>
@@ -86943,13 +86943,13 @@
     </row>
     <row r="1932" spans="1:14" ht="45">
       <c r="A1932" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1932" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1932" s="33" t="s">
+      <c r="C1932" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1932" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1932" s="34" t="s">
         <v>2</v>
@@ -86970,7 +86970,7 @@
         <v>181</v>
       </c>
       <c r="J1932" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1932" s="16" t="s">
         <v>296</v>
@@ -86979,7 +86979,7 @@
         <v>434</v>
       </c>
       <c r="M1932" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1932" s="23" t="s">
         <v>419</v>
@@ -86987,13 +86987,13 @@
     </row>
     <row r="1933" spans="1:14" ht="60">
       <c r="A1933" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1933" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1933" s="33" t="s">
+      <c r="C1933" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1933" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1933" s="34" t="s">
         <v>2</v>
@@ -87031,13 +87031,13 @@
     </row>
     <row r="1934" spans="1:14" ht="45">
       <c r="A1934" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1934" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1934" s="33" t="s">
+      <c r="C1934" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1934" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1934" s="34" t="s">
         <v>2</v>
@@ -87058,7 +87058,7 @@
         <v>181</v>
       </c>
       <c r="J1934" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1934" s="16" t="s">
         <v>296</v>
@@ -87067,7 +87067,7 @@
         <v>435</v>
       </c>
       <c r="M1934" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1934" s="23" t="s">
         <v>419</v>
@@ -87075,13 +87075,13 @@
     </row>
     <row r="1935" spans="1:14" ht="45">
       <c r="A1935" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1935" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1935" s="33" t="s">
+      <c r="C1935" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1935" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1935" s="34" t="s">
         <v>2</v>
@@ -87102,7 +87102,7 @@
         <v>181</v>
       </c>
       <c r="J1935" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1935" s="16" t="s">
         <v>296</v>
@@ -87111,7 +87111,7 @@
         <v>436</v>
       </c>
       <c r="M1935" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1935" s="23" t="s">
         <v>419</v>
@@ -87119,13 +87119,13 @@
     </row>
     <row r="1936" spans="1:14" ht="45">
       <c r="A1936" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1936" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1936" s="33" t="s">
+      <c r="C1936" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1936" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1936" s="34" t="s">
         <v>2</v>
@@ -87157,13 +87157,13 @@
     </row>
     <row r="1937" spans="1:14" ht="37.5" customHeight="1">
       <c r="A1937" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1937" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1937" s="33" t="s">
+      <c r="C1937" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1937" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1937" s="34" t="s">
         <v>2</v>
@@ -87184,7 +87184,7 @@
         <v>179</v>
       </c>
       <c r="J1937" s="18" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="K1937" s="16" t="s">
         <v>296</v>
@@ -87193,7 +87193,7 @@
         <v>505</v>
       </c>
       <c r="M1937" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N1937" s="23" t="s">
         <v>419</v>
@@ -87201,13 +87201,13 @@
     </row>
     <row r="1938" spans="1:14" ht="37.5" customHeight="1">
       <c r="A1938" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1938" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1938" s="33" t="s">
+      <c r="C1938" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1938" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1938" s="34" t="s">
         <v>2</v>
@@ -87228,7 +87228,7 @@
         <v>181</v>
       </c>
       <c r="J1938" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1938" s="16" t="s">
         <v>296</v>
@@ -87237,7 +87237,7 @@
         <v>505</v>
       </c>
       <c r="M1938" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1938" s="23" t="s">
         <v>419</v>
@@ -87245,13 +87245,13 @@
     </row>
     <row r="1939" spans="1:14" ht="45">
       <c r="A1939" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1939" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1939" s="33" t="s">
+      <c r="C1939" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1939" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1939" s="34" t="s">
         <v>2</v>
@@ -87289,13 +87289,13 @@
     </row>
     <row r="1940" spans="1:14" ht="45">
       <c r="A1940" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1940" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1940" s="33" t="s">
+      <c r="C1940" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1940" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1940" s="34" t="s">
         <v>2</v>
@@ -87316,7 +87316,7 @@
         <v>181</v>
       </c>
       <c r="J1940" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1940" s="16" t="s">
         <v>296</v>
@@ -87325,7 +87325,7 @@
         <v>507</v>
       </c>
       <c r="M1940" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1940" s="23" t="s">
         <v>419</v>
@@ -87333,13 +87333,13 @@
     </row>
     <row r="1941" spans="1:14" ht="45">
       <c r="A1941" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1941" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1941" s="33" t="s">
+      <c r="C1941" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1941" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1941" s="34" t="s">
         <v>2</v>
@@ -87360,7 +87360,7 @@
         <v>181</v>
       </c>
       <c r="J1941" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1941" s="16" t="s">
         <v>296</v>
@@ -87369,7 +87369,7 @@
         <v>438</v>
       </c>
       <c r="M1941" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1941" s="23" t="s">
         <v>419</v>
@@ -87377,13 +87377,13 @@
     </row>
     <row r="1942" spans="1:14" ht="45">
       <c r="A1942" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1942" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1942" s="33" t="s">
+      <c r="C1942" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1942" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1942" s="34" t="s">
         <v>2</v>
@@ -87404,7 +87404,7 @@
         <v>181</v>
       </c>
       <c r="J1942" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1942" s="16" t="s">
         <v>296</v>
@@ -87413,7 +87413,7 @@
         <v>439</v>
       </c>
       <c r="M1942" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1942" s="23" t="s">
         <v>419</v>
@@ -87421,13 +87421,13 @@
     </row>
     <row r="1943" spans="1:14" ht="75">
       <c r="A1943" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1943" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1943" s="33" t="s">
+      <c r="C1943" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1943" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1943" s="34" t="s">
         <v>2</v>
@@ -87448,7 +87448,7 @@
         <v>179</v>
       </c>
       <c r="J1943" s="18" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="K1943" s="16" t="s">
         <v>296</v>
@@ -87457,7 +87457,7 @@
         <v>509</v>
       </c>
       <c r="M1943" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N1943" s="23" t="s">
         <v>419</v>
@@ -87465,13 +87465,13 @@
     </row>
     <row r="1944" spans="1:14" ht="75">
       <c r="A1944" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1944" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1944" s="33" t="s">
+      <c r="C1944" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1944" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1944" s="34" t="s">
         <v>2</v>
@@ -87492,7 +87492,7 @@
         <v>181</v>
       </c>
       <c r="J1944" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1944" s="16" t="s">
         <v>296</v>
@@ -87501,7 +87501,7 @@
         <v>509</v>
       </c>
       <c r="M1944" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1944" s="23" t="s">
         <v>419</v>
@@ -87509,13 +87509,13 @@
     </row>
     <row r="1945" spans="1:14" ht="75">
       <c r="A1945" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1945" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1945" s="33" t="s">
+      <c r="C1945" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1945" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1945" s="34" t="s">
         <v>2</v>
@@ -87536,7 +87536,7 @@
         <v>179</v>
       </c>
       <c r="J1945" s="18" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="K1945" s="16" t="s">
         <v>296</v>
@@ -87545,7 +87545,7 @@
         <v>597</v>
       </c>
       <c r="M1945" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N1945" s="23" t="s">
         <v>419</v>
@@ -87553,13 +87553,13 @@
     </row>
     <row r="1946" spans="1:14" ht="75">
       <c r="A1946" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1946" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1946" s="33" t="s">
+      <c r="C1946" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1946" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1946" s="34" t="s">
         <v>2</v>
@@ -87580,7 +87580,7 @@
         <v>181</v>
       </c>
       <c r="J1946" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1946" s="16" t="s">
         <v>296</v>
@@ -87589,7 +87589,7 @@
         <v>597</v>
       </c>
       <c r="M1946" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1946" s="23" t="s">
         <v>419</v>
@@ -87597,13 +87597,13 @@
     </row>
     <row r="1947" spans="1:14" ht="105">
       <c r="A1947" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1947" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1947" s="33" t="s">
+      <c r="C1947" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1947" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1947" s="34" t="s">
         <v>2</v>
@@ -87615,7 +87615,7 @@
         <v>106</v>
       </c>
       <c r="G1947" s="36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1947" s="94">
         <v>100</v>
@@ -87641,13 +87641,13 @@
     </row>
     <row r="1948" spans="1:14" ht="105">
       <c r="A1948" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1948" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1948" s="33" t="s">
+      <c r="C1948" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1948" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1948" s="34" t="s">
         <v>2</v>
@@ -87659,7 +87659,7 @@
         <v>106</v>
       </c>
       <c r="G1948" s="36" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1948" s="94">
         <v>100</v>
@@ -87668,7 +87668,7 @@
         <v>181</v>
       </c>
       <c r="J1948" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1948" s="16" t="s">
         <v>296</v>
@@ -87677,7 +87677,7 @@
         <v>510</v>
       </c>
       <c r="M1948" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1948" s="23" t="s">
         <v>419</v>
@@ -87685,13 +87685,13 @@
     </row>
     <row r="1949" spans="1:14" ht="105">
       <c r="A1949" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1949" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1949" s="33" t="s">
+      <c r="C1949" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1949" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1949" s="34" t="s">
         <v>2</v>
@@ -87712,7 +87712,7 @@
         <v>181</v>
       </c>
       <c r="J1949" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1949" s="16" t="s">
         <v>296</v>
@@ -87721,7 +87721,7 @@
         <v>512</v>
       </c>
       <c r="M1949" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1949" s="23" t="s">
         <v>419</v>
@@ -87729,13 +87729,13 @@
     </row>
     <row r="1950" spans="1:14" ht="45">
       <c r="A1950" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1950" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1950" s="33" t="s">
+      <c r="C1950" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1950" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1950" s="34" t="s">
         <v>2</v>
@@ -87756,7 +87756,7 @@
         <v>181</v>
       </c>
       <c r="J1950" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1950" s="16" t="s">
         <v>296</v>
@@ -87765,7 +87765,7 @@
         <v>611</v>
       </c>
       <c r="M1950" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1950" s="23" t="s">
         <v>419</v>
@@ -87773,13 +87773,13 @@
     </row>
     <row r="1951" spans="1:14" ht="45">
       <c r="A1951" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1951" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1951" s="33" t="s">
+      <c r="C1951" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1951" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1951" s="34" t="s">
         <v>2</v>
@@ -87817,13 +87817,13 @@
     </row>
     <row r="1952" spans="1:14" ht="45">
       <c r="A1952" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1952" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1952" s="33" t="s">
+      <c r="C1952" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1952" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1952" s="34" t="s">
         <v>2</v>
@@ -87844,7 +87844,7 @@
         <v>181</v>
       </c>
       <c r="J1952" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1952" s="16" t="s">
         <v>296</v>
@@ -87853,7 +87853,7 @@
         <v>582</v>
       </c>
       <c r="M1952" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1952" s="23" t="s">
         <v>419</v>
@@ -87861,13 +87861,13 @@
     </row>
     <row r="1953" spans="1:14" ht="45">
       <c r="A1953" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1953" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1953" s="33" t="s">
+      <c r="C1953" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1953" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1953" s="34" t="s">
         <v>2</v>
@@ -87905,13 +87905,13 @@
     </row>
     <row r="1954" spans="1:14" ht="45">
       <c r="A1954" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1954" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1954" s="33" t="s">
+      <c r="C1954" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1954" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1954" s="34" t="s">
         <v>2</v>
@@ -87932,7 +87932,7 @@
         <v>181</v>
       </c>
       <c r="J1954" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1954" s="16" t="s">
         <v>296</v>
@@ -87941,7 +87941,7 @@
         <v>513</v>
       </c>
       <c r="M1954" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1954" s="23" t="s">
         <v>419</v>
@@ -87949,13 +87949,13 @@
     </row>
     <row r="1955" spans="1:14" ht="45">
       <c r="A1955" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1955" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1955" s="33" t="s">
+      <c r="C1955" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1955" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1955" s="34" t="s">
         <v>2</v>
@@ -87976,7 +87976,7 @@
         <v>181</v>
       </c>
       <c r="J1955" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1955" s="16" t="s">
         <v>296</v>
@@ -87985,7 +87985,7 @@
         <v>622</v>
       </c>
       <c r="M1955" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1955" s="23" t="s">
         <v>419</v>
@@ -87993,13 +87993,13 @@
     </row>
     <row r="1956" spans="1:14" ht="45">
       <c r="A1956" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1956" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1956" s="33" t="s">
+      <c r="C1956" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1956" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1956" s="34" t="s">
         <v>2</v>
@@ -88037,13 +88037,13 @@
     </row>
     <row r="1957" spans="1:14" ht="45">
       <c r="A1957" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1957" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1957" s="33" t="s">
+      <c r="C1957" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1957" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1957" s="34" t="s">
         <v>2</v>
@@ -88064,7 +88064,7 @@
         <v>181</v>
       </c>
       <c r="J1957" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1957" s="16" t="s">
         <v>296</v>
@@ -88073,7 +88073,7 @@
         <v>516</v>
       </c>
       <c r="M1957" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1957" s="23" t="s">
         <v>419</v>
@@ -88081,13 +88081,13 @@
     </row>
     <row r="1958" spans="1:14" ht="45">
       <c r="A1958" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1958" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1958" s="33" t="s">
+      <c r="C1958" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1958" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1958" s="34" t="s">
         <v>2</v>
@@ -88108,7 +88108,7 @@
         <v>181</v>
       </c>
       <c r="J1958" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1958" s="16" t="s">
         <v>296</v>
@@ -88117,7 +88117,7 @@
         <v>517</v>
       </c>
       <c r="M1958" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1958" s="23" t="s">
         <v>419</v>
@@ -88125,13 +88125,13 @@
     </row>
     <row r="1959" spans="1:14" ht="45">
       <c r="A1959" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1959" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1959" s="33" t="s">
+      <c r="C1959" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1959" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1959" s="34" t="s">
         <v>2</v>
@@ -88163,13 +88163,13 @@
     </row>
     <row r="1960" spans="1:14" ht="45">
       <c r="A1960" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1960" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1960" s="33" t="s">
+      <c r="C1960" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1960" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1960" s="34" t="s">
         <v>2</v>
@@ -88190,7 +88190,7 @@
         <v>181</v>
       </c>
       <c r="J1960" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1960" s="16" t="s">
         <v>296</v>
@@ -88199,7 +88199,7 @@
         <v>521</v>
       </c>
       <c r="M1960" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1960" s="23" t="s">
         <v>419</v>
@@ -88207,13 +88207,13 @@
     </row>
     <row r="1961" spans="1:14" ht="45">
       <c r="A1961" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1961" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1961" s="33" t="s">
+      <c r="C1961" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1961" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1961" s="34" t="s">
         <v>2</v>
@@ -88234,7 +88234,7 @@
         <v>181</v>
       </c>
       <c r="J1961" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1961" s="16" t="s">
         <v>296</v>
@@ -88243,7 +88243,7 @@
         <v>599</v>
       </c>
       <c r="M1961" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1961" s="23" t="s">
         <v>419</v>
@@ -88251,13 +88251,13 @@
     </row>
     <row r="1962" spans="1:14" ht="45">
       <c r="A1962" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1962" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1962" s="33" t="s">
+      <c r="C1962" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1962" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1962" s="34" t="s">
         <v>2</v>
@@ -88278,7 +88278,7 @@
         <v>181</v>
       </c>
       <c r="J1962" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K1962" s="16" t="s">
         <v>296</v>
@@ -88287,7 +88287,7 @@
         <v>600</v>
       </c>
       <c r="M1962" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N1962" s="23" t="s">
         <v>419</v>
@@ -88295,13 +88295,13 @@
     </row>
     <row r="1963" spans="1:14" ht="45">
       <c r="A1963" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1963" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1963" s="33" t="s">
+      <c r="C1963" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1963" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1963" s="34" t="s">
         <v>2</v>
@@ -88339,13 +88339,13 @@
     </row>
     <row r="1964" spans="1:14" ht="45">
       <c r="A1964" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1964" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1964" s="33" t="s">
+      <c r="C1964" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1964" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1964" s="34" t="s">
         <v>2</v>
@@ -88383,13 +88383,13 @@
     </row>
     <row r="1965" spans="1:14" ht="45">
       <c r="A1965" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1965" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1965" s="33" t="s">
+      <c r="C1965" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1965" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1965" s="34" t="s">
         <v>2</v>
@@ -88410,7 +88410,7 @@
         <v>94</v>
       </c>
       <c r="J1965" s="18" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="K1965" s="16" t="s">
         <v>296</v>
@@ -88419,7 +88419,7 @@
         <v>602</v>
       </c>
       <c r="M1965" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N1965" s="23" t="s">
         <v>419</v>
@@ -88427,13 +88427,13 @@
     </row>
     <row r="1966" spans="1:14" ht="45">
       <c r="A1966" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1966" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1966" s="33" t="s">
+      <c r="C1966" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1966" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1966" s="34" t="s">
         <v>2</v>
@@ -88471,13 +88471,13 @@
     </row>
     <row r="1967" spans="1:14" ht="45">
       <c r="A1967" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1967" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1967" s="33" t="s">
+      <c r="C1967" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1967" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1967" s="34" t="s">
         <v>2</v>
@@ -88515,13 +88515,13 @@
     </row>
     <row r="1968" spans="1:14" ht="45">
       <c r="A1968" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1968" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1968" s="33" t="s">
+      <c r="C1968" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1968" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1968" s="34" t="s">
         <v>2</v>
@@ -88559,13 +88559,13 @@
     </row>
     <row r="1969" spans="1:14" ht="45">
       <c r="A1969" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1969" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1969" s="33" t="s">
+      <c r="C1969" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1969" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1969" s="34" t="s">
         <v>2</v>
@@ -88603,13 +88603,13 @@
     </row>
     <row r="1970" spans="1:14" ht="45">
       <c r="A1970" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1970" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1970" s="33" t="s">
+      <c r="C1970" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1970" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1970" s="34" t="s">
         <v>2</v>
@@ -88647,13 +88647,13 @@
     </row>
     <row r="1971" spans="1:14" ht="45">
       <c r="A1971" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1971" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1971" s="33" t="s">
+      <c r="C1971" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1971" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1971" s="34" t="s">
         <v>2</v>
@@ -88691,13 +88691,13 @@
     </row>
     <row r="1972" spans="1:14" ht="45">
       <c r="A1972" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1972" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1972" s="33" t="s">
+      <c r="C1972" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1972" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1972" s="34" t="s">
         <v>2</v>
@@ -88735,13 +88735,13 @@
     </row>
     <row r="1973" spans="1:14" ht="45">
       <c r="A1973" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1973" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1973" s="33" t="s">
+      <c r="C1973" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1973" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1973" s="34" t="s">
         <v>2</v>
@@ -88775,13 +88775,13 @@
     </row>
     <row r="1974" spans="1:14" ht="45">
       <c r="A1974" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1974" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1974" s="33" t="s">
+      <c r="C1974" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1974" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1974" s="34" t="s">
         <v>2</v>
@@ -88819,13 +88819,13 @@
     </row>
     <row r="1975" spans="1:14" ht="45">
       <c r="A1975" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1975" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1975" s="33" t="s">
+      <c r="C1975" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1975" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1975" s="34" t="s">
         <v>2</v>
@@ -88863,13 +88863,13 @@
     </row>
     <row r="1976" spans="1:14" ht="45">
       <c r="A1976" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1976" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1976" s="33" t="s">
+      <c r="C1976" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1976" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1976" s="34" t="s">
         <v>2</v>
@@ -88907,13 +88907,13 @@
     </row>
     <row r="1977" spans="1:14" ht="45">
       <c r="A1977" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1977" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1977" s="33" t="s">
+      <c r="C1977" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1977" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1977" s="34" t="s">
         <v>2</v>
@@ -88951,13 +88951,13 @@
     </row>
     <row r="1978" spans="1:14" ht="45">
       <c r="A1978" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1978" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1978" s="33" t="s">
+      <c r="C1978" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1978" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1978" s="34" t="s">
         <v>2</v>
@@ -88995,13 +88995,13 @@
     </row>
     <row r="1979" spans="1:14" ht="45">
       <c r="A1979" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1979" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1979" s="33" t="s">
+      <c r="C1979" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1979" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1979" s="34" t="s">
         <v>2</v>
@@ -89033,13 +89033,13 @@
     </row>
     <row r="1980" spans="1:14" ht="45">
       <c r="A1980" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1980" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1980" s="33" t="s">
+      <c r="C1980" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1980" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1980" s="34" t="s">
         <v>2</v>
@@ -89077,13 +89077,13 @@
     </row>
     <row r="1981" spans="1:14" ht="45">
       <c r="A1981" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1981" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1981" s="33" t="s">
+      <c r="C1981" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1981" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1981" s="34" t="s">
         <v>2</v>
@@ -89121,13 +89121,13 @@
     </row>
     <row r="1982" spans="1:14" ht="60">
       <c r="A1982" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1982" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1982" s="33" t="s">
+      <c r="C1982" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1982" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1982" s="34" t="s">
         <v>2</v>
@@ -89165,13 +89165,13 @@
     </row>
     <row r="1983" spans="1:14" ht="60">
       <c r="A1983" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1983" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1983" s="33" t="s">
+      <c r="C1983" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1983" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1983" s="34" t="s">
         <v>2</v>
@@ -89209,13 +89209,13 @@
     </row>
     <row r="1984" spans="1:14" ht="60">
       <c r="A1984" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1984" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1984" s="33" t="s">
+      <c r="C1984" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1984" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1984" s="34" t="s">
         <v>2</v>
@@ -89253,13 +89253,13 @@
     </row>
     <row r="1985" spans="1:14" ht="60">
       <c r="A1985" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1985" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1985" s="33" t="s">
+      <c r="C1985" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1985" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1985" s="34" t="s">
         <v>2</v>
@@ -89297,13 +89297,13 @@
     </row>
     <row r="1986" spans="1:14" ht="60">
       <c r="A1986" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1986" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1986" s="33" t="s">
+      <c r="C1986" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1986" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1986" s="34" t="s">
         <v>2</v>
@@ -89341,13 +89341,13 @@
     </row>
     <row r="1987" spans="1:14" ht="60">
       <c r="A1987" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1987" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1987" s="33" t="s">
+      <c r="C1987" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1987" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1987" s="34" t="s">
         <v>2</v>
@@ -89385,13 +89385,13 @@
     </row>
     <row r="1988" spans="1:14" ht="60">
       <c r="A1988" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1988" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1988" s="33" t="s">
+      <c r="C1988" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1988" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1988" s="34" t="s">
         <v>2</v>
@@ -89429,13 +89429,13 @@
     </row>
     <row r="1989" spans="1:14" ht="60">
       <c r="A1989" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1989" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1989" s="33" t="s">
+      <c r="C1989" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1989" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1989" s="34" t="s">
         <v>2</v>
@@ -89473,13 +89473,13 @@
     </row>
     <row r="1990" spans="1:14" ht="45">
       <c r="A1990" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1990" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1990" s="33" t="s">
+      <c r="C1990" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1990" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1990" s="34" t="s">
         <v>2</v>
@@ -89517,13 +89517,13 @@
     </row>
     <row r="1991" spans="1:14" ht="45">
       <c r="A1991" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1991" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1991" s="33" t="s">
+      <c r="C1991" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1991" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1991" s="34" t="s">
         <v>2</v>
@@ -89561,13 +89561,13 @@
     </row>
     <row r="1992" spans="1:14" ht="75">
       <c r="A1992" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1992" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1992" s="33" t="s">
+      <c r="C1992" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1992" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1992" s="34" t="s">
         <v>2</v>
@@ -89605,13 +89605,13 @@
     </row>
     <row r="1993" spans="1:14" ht="60">
       <c r="A1993" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1993" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1993" s="33" t="s">
+      <c r="C1993" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1993" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1993" s="34" t="s">
         <v>2</v>
@@ -89649,13 +89649,13 @@
     </row>
     <row r="1994" spans="1:14" ht="60">
       <c r="A1994" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1994" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1994" s="33" t="s">
+      <c r="C1994" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1994" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1994" s="34" t="s">
         <v>2</v>
@@ -89693,13 +89693,13 @@
     </row>
     <row r="1995" spans="1:14" ht="60">
       <c r="A1995" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1995" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1995" s="33" t="s">
+      <c r="C1995" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1995" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1995" s="34" t="s">
         <v>2</v>
@@ -89737,13 +89737,13 @@
     </row>
     <row r="1996" spans="1:14" ht="60">
       <c r="A1996" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1996" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1996" s="33" t="s">
+      <c r="C1996" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1996" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1996" s="34" t="s">
         <v>2</v>
@@ -89781,13 +89781,13 @@
     </row>
     <row r="1997" spans="1:14" ht="60">
       <c r="A1997" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1997" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1997" s="33" t="s">
+      <c r="C1997" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1997" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1997" s="34" t="s">
         <v>2</v>
@@ -89825,13 +89825,13 @@
     </row>
     <row r="1998" spans="1:14" ht="60">
       <c r="A1998" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1998" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1998" s="33" t="s">
+      <c r="C1998" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1998" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1998" s="34" t="s">
         <v>2</v>
@@ -89869,13 +89869,13 @@
     </row>
     <row r="1999" spans="1:14" ht="60">
       <c r="A1999" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1999" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B1999" s="33" t="s">
+      <c r="C1999" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C1999" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D1999" s="34" t="s">
         <v>2</v>
@@ -89913,13 +89913,13 @@
     </row>
     <row r="2000" spans="1:14" ht="45">
       <c r="A2000" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2000" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2000" s="33" t="s">
+      <c r="C2000" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2000" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2000" s="34" t="s">
         <v>2</v>
@@ -89957,13 +89957,13 @@
     </row>
     <row r="2001" spans="1:14" ht="45">
       <c r="A2001" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2001" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2001" s="33" t="s">
+      <c r="C2001" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2001" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2001" s="34" t="s">
         <v>2</v>
@@ -89984,7 +89984,7 @@
         <v>181</v>
       </c>
       <c r="J2001" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2001" s="16" t="s">
         <v>296</v>
@@ -89993,7 +89993,7 @@
         <v>441</v>
       </c>
       <c r="M2001" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2001" s="23" t="s">
         <v>419</v>
@@ -90001,13 +90001,13 @@
     </row>
     <row r="2002" spans="1:14" ht="45">
       <c r="A2002" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2002" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2002" s="33" t="s">
+      <c r="C2002" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2002" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2002" s="34" t="s">
         <v>2</v>
@@ -90028,7 +90028,7 @@
         <v>181</v>
       </c>
       <c r="J2002" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2002" s="16" t="s">
         <v>296</v>
@@ -90037,7 +90037,7 @@
         <v>444</v>
       </c>
       <c r="M2002" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2002" s="23" t="s">
         <v>419</v>
@@ -90045,13 +90045,13 @@
     </row>
     <row r="2003" spans="1:14" ht="45">
       <c r="A2003" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2003" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2003" s="33" t="s">
+      <c r="C2003" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2003" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2003" s="34" t="s">
         <v>2</v>
@@ -90072,7 +90072,7 @@
         <v>181</v>
       </c>
       <c r="J2003" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2003" s="16" t="s">
         <v>296</v>
@@ -90081,7 +90081,7 @@
         <v>420</v>
       </c>
       <c r="M2003" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2003" s="23" t="s">
         <v>419</v>
@@ -90089,13 +90089,13 @@
     </row>
     <row r="2004" spans="1:14" ht="45">
       <c r="A2004" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2004" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2004" s="33" t="s">
+      <c r="C2004" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2004" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2004" s="34" t="s">
         <v>2</v>
@@ -90113,7 +90113,7 @@
         <v>500</v>
       </c>
       <c r="I2004" s="30" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J2004" s="46" t="s">
         <v>738</v>
@@ -90125,7 +90125,7 @@
         <v>420</v>
       </c>
       <c r="M2004" s="55" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="N2004" s="23" t="s">
         <v>419</v>
@@ -90133,13 +90133,13 @@
     </row>
     <row r="2005" spans="1:14" ht="45">
       <c r="A2005" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2005" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2005" s="33" t="s">
+      <c r="C2005" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2005" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2005" s="34" t="s">
         <v>2</v>
@@ -90160,7 +90160,7 @@
         <v>181</v>
       </c>
       <c r="J2005" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2005" s="16" t="s">
         <v>296</v>
@@ -90169,7 +90169,7 @@
         <v>628</v>
       </c>
       <c r="M2005" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2005" s="23" t="s">
         <v>419</v>
@@ -90177,13 +90177,13 @@
     </row>
     <row r="2006" spans="1:14" ht="45">
       <c r="A2006" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2006" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2006" s="33" t="s">
+      <c r="C2006" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2006" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2006" s="34" t="s">
         <v>2</v>
@@ -90204,7 +90204,7 @@
         <v>181</v>
       </c>
       <c r="J2006" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2006" s="16" t="s">
         <v>296</v>
@@ -90213,7 +90213,7 @@
         <v>684</v>
       </c>
       <c r="M2006" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2006" s="23" t="s">
         <v>419</v>
@@ -90221,13 +90221,13 @@
     </row>
     <row r="2007" spans="1:14" ht="45">
       <c r="A2007" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2007" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2007" s="33" t="s">
+      <c r="C2007" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2007" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2007" s="34" t="s">
         <v>2</v>
@@ -90248,7 +90248,7 @@
         <v>181</v>
       </c>
       <c r="J2007" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2007" s="16" t="s">
         <v>296</v>
@@ -90257,7 +90257,7 @@
         <v>687</v>
       </c>
       <c r="M2007" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2007" s="23" t="s">
         <v>419</v>
@@ -90265,13 +90265,13 @@
     </row>
     <row r="2008" spans="1:14" ht="75">
       <c r="A2008" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2008" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2008" s="33" t="s">
+      <c r="C2008" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2008" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2008" s="34" t="s">
         <v>2</v>
@@ -90303,13 +90303,13 @@
     </row>
     <row r="2009" spans="1:14" ht="45">
       <c r="A2009" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2009" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2009" s="33" t="s">
+      <c r="C2009" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2009" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2009" s="34" t="s">
         <v>2</v>
@@ -90330,7 +90330,7 @@
         <v>181</v>
       </c>
       <c r="J2009" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2009" s="16" t="s">
         <v>296</v>
@@ -90339,7 +90339,7 @@
         <v>447</v>
       </c>
       <c r="M2009" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2009" s="23" t="s">
         <v>419</v>
@@ -90347,13 +90347,13 @@
     </row>
     <row r="2010" spans="1:14" ht="45">
       <c r="A2010" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2010" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2010" s="33" t="s">
+      <c r="C2010" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2010" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2010" s="34" t="s">
         <v>2</v>
@@ -90374,7 +90374,7 @@
         <v>181</v>
       </c>
       <c r="J2010" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2010" s="16" t="s">
         <v>296</v>
@@ -90383,7 +90383,7 @@
         <v>448</v>
       </c>
       <c r="M2010" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2010" s="23" t="s">
         <v>419</v>
@@ -90391,13 +90391,13 @@
     </row>
     <row r="2011" spans="1:14" ht="60">
       <c r="A2011" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2011" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2011" s="33" t="s">
+      <c r="C2011" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2011" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2011" s="34" t="s">
         <v>2</v>
@@ -90418,7 +90418,7 @@
         <v>181</v>
       </c>
       <c r="J2011" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2011" s="16" t="s">
         <v>296</v>
@@ -90427,7 +90427,7 @@
         <v>449</v>
       </c>
       <c r="M2011" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2011" s="23" t="s">
         <v>419</v>
@@ -90435,13 +90435,13 @@
     </row>
     <row r="2012" spans="1:14" ht="45">
       <c r="A2012" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2012" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2012" s="33" t="s">
+      <c r="C2012" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2012" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2012" s="34" t="s">
         <v>2</v>
@@ -90462,7 +90462,7 @@
         <v>181</v>
       </c>
       <c r="J2012" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2012" s="16" t="s">
         <v>296</v>
@@ -90471,7 +90471,7 @@
         <v>450</v>
       </c>
       <c r="M2012" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2012" s="23" t="s">
         <v>419</v>
@@ -90479,13 +90479,13 @@
     </row>
     <row r="2013" spans="1:14" ht="60">
       <c r="A2013" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2013" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2013" s="33" t="s">
+      <c r="C2013" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2013" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2013" s="34" t="s">
         <v>2</v>
@@ -90506,7 +90506,7 @@
         <v>181</v>
       </c>
       <c r="J2013" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2013" s="16" t="s">
         <v>296</v>
@@ -90515,7 +90515,7 @@
         <v>576</v>
       </c>
       <c r="M2013" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2013" s="23" t="s">
         <v>419</v>
@@ -90523,13 +90523,13 @@
     </row>
     <row r="2014" spans="1:14" ht="45">
       <c r="A2014" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2014" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2014" s="33" t="s">
+      <c r="C2014" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2014" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2014" s="34" t="s">
         <v>2</v>
@@ -90550,7 +90550,7 @@
         <v>181</v>
       </c>
       <c r="J2014" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2014" s="16" t="s">
         <v>296</v>
@@ -90559,7 +90559,7 @@
         <v>577</v>
       </c>
       <c r="M2014" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2014" s="23" t="s">
         <v>419</v>
@@ -90567,13 +90567,13 @@
     </row>
     <row r="2015" spans="1:14" ht="45">
       <c r="A2015" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2015" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2015" s="33" t="s">
+      <c r="C2015" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2015" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2015" s="34" t="s">
         <v>2</v>
@@ -90594,7 +90594,7 @@
         <v>181</v>
       </c>
       <c r="J2015" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2015" s="16" t="s">
         <v>296</v>
@@ -90603,7 +90603,7 @@
         <v>578</v>
       </c>
       <c r="M2015" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2015" s="23" t="s">
         <v>419</v>
@@ -90611,13 +90611,13 @@
     </row>
     <row r="2016" spans="1:14" ht="45">
       <c r="A2016" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2016" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2016" s="33" t="s">
+      <c r="C2016" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2016" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2016" s="34" t="s">
         <v>2</v>
@@ -90638,7 +90638,7 @@
         <v>181</v>
       </c>
       <c r="J2016" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2016" s="16" t="s">
         <v>296</v>
@@ -90647,7 +90647,7 @@
         <v>594</v>
       </c>
       <c r="M2016" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2016" s="23" t="s">
         <v>419</v>
@@ -90655,13 +90655,13 @@
     </row>
     <row r="2017" spans="1:14" ht="45">
       <c r="A2017" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2017" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2017" s="33" t="s">
+      <c r="C2017" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2017" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2017" s="34" t="s">
         <v>2</v>
@@ -90682,7 +90682,7 @@
         <v>181</v>
       </c>
       <c r="J2017" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2017" s="16" t="s">
         <v>296</v>
@@ -90691,7 +90691,7 @@
         <v>579</v>
       </c>
       <c r="M2017" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2017" s="23" t="s">
         <v>419</v>
@@ -90699,13 +90699,13 @@
     </row>
     <row r="2018" spans="1:14" ht="45">
       <c r="A2018" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2018" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2018" s="33" t="s">
+      <c r="C2018" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2018" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2018" s="34" t="s">
         <v>2</v>
@@ -90726,7 +90726,7 @@
         <v>181</v>
       </c>
       <c r="J2018" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2018" s="16" t="s">
         <v>296</v>
@@ -90735,7 +90735,7 @@
         <v>452</v>
       </c>
       <c r="M2018" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2018" s="23" t="s">
         <v>419</v>
@@ -90743,13 +90743,13 @@
     </row>
     <row r="2019" spans="1:14" ht="45">
       <c r="A2019" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2019" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2019" s="33" t="s">
+      <c r="C2019" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2019" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2019" s="34" t="s">
         <v>2</v>
@@ -90770,7 +90770,7 @@
         <v>181</v>
       </c>
       <c r="J2019" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K2019" s="16" t="s">
         <v>296</v>
@@ -90779,7 +90779,7 @@
         <v>453</v>
       </c>
       <c r="M2019" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N2019" s="23" t="s">
         <v>419</v>
@@ -90787,13 +90787,13 @@
     </row>
     <row r="2020" spans="1:14" ht="45">
       <c r="A2020" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2020" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="B2020" s="33" t="s">
+      <c r="C2020" s="33" t="s">
         <v>756</v>
-      </c>
-      <c r="C2020" s="33" t="s">
-        <v>757</v>
       </c>
       <c r="D2020" s="34" t="s">
         <v>2</v>
